--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/text_comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/text_comparison.xlsx
@@ -34,7 +34,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,12 @@
         <bgColor rgb="00FDEBD0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+        <bgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -84,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +102,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -568,8 +577,8 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Une mise à jour de la ligne directrice sur la gestion des risques climatiques a été publiée, incluant des modifications sur la divulgation des émissions de GES. Ce changement est substantiel car il modifie les exigences de divulgation, impactant potentiellement la stratégie de gestion des risques climatiques de la banque. Cela implique que la banque doit escalader cette information pour ajuster ses pratiques de gestion des risques climatiques
-Les modifications des exigences de divulgation des GES nécessitent une révision des pratiques de gestion des risques climatiques</t>
+          <t>Une mise à jour de la ligne directrice sur la gestion des risques climatiques a été publiée, reportant l'exigence de divulgation des émissions de GES de portée trois. Ce changement est substantiel car il modifie les attentes réglementaires en matière de divulgation, ce qui peut affecter la stratégie de gestion des risques climatiques de la banque. Cela nécessite une escalade pour comprendre l'impact de ce report sur la conformité et la gestion des risques climatiques
+Modification des attentes réglementaires en matière de divulgation des émissions de GES, impactant la stratégie de gestion des risques climatiques</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -610,7 +619,7 @@
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>La banque a émis un total de actions ordinaires pour un produit brut de G$ lors de l'acquisition de CWB. Ce changement est substantiel car il modifie significativement la structure du capital de la banque. Cela implique une surveillance accrue des impacts sur les ratios de capital et la dilution potentielle des actions existantes
-Augmentation significative du capital social et potentiel impact dilutif sur les actions existantes</t>
+Augmentation significative du capital social et potentiel de dilution des actions existantes</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -623,13 +632,13 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Risque environnemental et social</t>
+          <t>Revenus de négociation et de souscription quotidiens</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -640,7 +649,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Le 23 avril 2025, les ACVM ont annoncé la suspension de leurs travaux sur les projets concernant la communication obligatoire d'information liée au changement climatique et les modifications des obligations d'information existantes sur la diversité. Les ACVM suivront l'évolution de la réglementation et revisiteront ces deux projets au cours des prochaines années.</t>
+          <t>Le graphique suivant illustre les revenus de négociation et de souscription ainsi que la VaR sur une base quotidienne. Les revenus de négociation et de souscription quotidiens ont été positifs pendant 98 % des jours du trimestre terminé le 30 avril 2025. De plus, un jour a été marqué par des pertes nettes de négociation et de souscription quotidiennes supérieures à 1 M$. Aucune de ces pertes n'excédaient la VaR.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -650,8 +659,8 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Les ACVM ont annoncé la suspension de projets sur la communication d'information climatique et la diversité. Ce changement est substantiel car il peut influencer les obligations de divulgation futures de la banque. Cela implique que la banque doit rester informée des évolutions réglementaires pour ajuster ses pratiques de divulgation
-La suspension des projets par les ACVM peut affecter les obligations de divulgation futures, nécessitant une veille réglementaire</t>
+          <t>Une nouvelle sous section a été ajoutée pour illustrer les revenus de négociation et de souscription quotidiens. Ce changement est substantiel car il fournit des informations supplémentaires sur la performance quotidienne des activités de négociation, ce qui peut influencer l'évaluation des risques de marché. Cela nécessite une investigation pour comprendre comment ces informations peuvent être intégrées dans les stratégies de gestion des risques
+Ajout d'informations sur la performance quotidienne des activités de négociation, influençant l'évaluation des risques de marché</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -659,18 +668,18 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Revenus de négociation et de souscription quotidiens</t>
+          <t>Activités de gestion</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -681,7 +690,7 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Le graphique suivant illustre les revenus de négociation et de souscription ainsi que la VaR sur une base quotidienne. Les revenus de négociation et de souscription quotidiens ont été positifs pendant 98 % des jours du trimestre terminé le 30 avril 2025. De plus, un jour a été marqué par des pertes nettes de négociation et de souscription quotidiennes supérieures à 1 M$. Aucune de ces pertes n'excédaient la VaR.</t>
+          <t>Le 3 février 2025, dans le cadre de l'acquisition de CWB, la Banque a acquis les obligations liées aux dettes subordonnées de CWB pour un montant total de 525 M$, qui incluait une débenture de 125 M$ portant intérêt à 4,840 % et échéant le 29 juin 2030 (le 2 mai 2025, la Banque a informé les détenteurs de son intention de racheter les débentures le 29 juin 2025, à un prix de rachat égal au capital impayé plus l'intérêt couru et impayé), une débenture de 150 M$ portant intérêt à 5,937 % et échéant le 22 décembre 2032 et une débenture de 250 M$ portant intérêt à 5,949 % et échéant le 29 janvier 2034. Comme les débentures respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -691,8 +700,8 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Une nouvelle sous section sur les revenus de négociation et de souscription quotidiens a été ajoutée. Ce changement est substantiel car il fournit des informations détaillées sur la performance quotidienne, ce qui peut influencer l'évaluation du risque de marché. Cela implique que la banque doit analyser ces données pour ajuster ses stratégies de gestion du risque de marché
-L'ajout de données sur les revenus quotidiens de négociation et de souscription peut influencer l'évaluation du risque de marché</t>
+          <t>La banque a acquis des obligations liées aux dettes subordonnées de CWB pour un montant total de M$. Ce changement est substantiel car il affecte la composition des fonds propres réglementaires de la banque. Cela nécessite une évaluation de l'impact sur les ratios de capital et la conformité réglementaire
+Modification de la composition des fonds propres réglementaires avec des implications sur les ratios de capital</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -722,7 +731,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Le 3 février 2025, dans le cadre de l'acquisition de CWB, la Banque a acquis les obligations liées aux dettes subordonnées de CWB pour un montant total de 525 M$, qui incluait une débenture de 125 M$ portant intérêt à 4,840 % et échéant le 29 juin 2030 (le 2 mai 2025, la Banque a informé les détenteurs de son intention de racheter les débentures le 29 juin 2025, à un prix de rachat égal au capital impayé plus l'intérêt couru et impayé), une débenture de 150 M$ portant intérêt à 5,937 % et échéant le 22 décembre 2032 et une débenture de 250 M$ portant intérêt à 5,949 % et échéant le 29 janvier 2034. Comme les débentures respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
+          <t>Le 20 février 2025, il y a eu un échange de la totalité des actions privilégiées de premier rang, série 5 et série 9, émises et en circulation de CWB, contre des actions privilégiées de premier rang essentiellement équivalentes de la Banque Nationale, série 47 et série 49, donnant droit à un dividende non cumulatif à taux rajusté tous les cinq ans, portant intérêt à 6,371 % et 7,651 %. La Banque a échangé 10 000 000 actions privilégiées pour un montant total de 264 M$. Comme les actions privilégiées, série 47 et série 49, respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -732,52 +741,60 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>La banque a acquis des obligations liées aux dettes subordonnées de CWB pour un montant total de M$. Ce changement est substantiel car il affecte la composition des fonds propres réglementaires de la banque. Cela nécessite une vérification de l'impact sur les ratios de fonds propres et la conformité réglementaire
-Modification de la composition des fonds propres réglementaires avec des implications sur les ratios de capital</t>
+          <t>Un échange d'actions privilégiées de CWB contre celles de la Banque Nationale a eu lieu. Ce changement est substantiel car il modifie la structure des fonds propres et peut affecter les ratios de capital. Cela nécessite une évaluation de l'impact sur la structure du capital et la conformité réglementaire
+Modification de la structure des fonds propres avec des implications sur les ratios de capital</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Activités de gestion</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Le 20 février 2025, il y a eu un échange de la totalité des actions privilégiées de premier rang, série 5 et série 9, émises et en circulation de CWB, contre des actions privilégiées de premier rang essentiellement équivalentes de la Banque Nationale, série 47 et série 49, donnant droit à un dividende non cumulatif à taux rajusté tous les cinq ans, portant intérêt à 6,371 % et 7,651 %. La Banque a échangé 10 000 000 actions privilégiées pour un montant total de 264 M$. Comme les actions privilégiées, série 47 et série 49, respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Un échange d'actions privilégiées de CWB contre celles de la Banque Nationale a eu lieu, totalisant un montant de M$. Ce changement est substantiel car il modifie la structure des fonds propres de la banque. Cela nécessite une évaluation de l'impact sur les ratios de capital et la conformité réglementaire
-Changement dans la structure des fonds propres avec des implications sur les ratios de capital</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Risque environnemental et social</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Le 18 décembre 2024, le Conseil canadien des normes d'information sur la durabilité (CCNID) a publié ses premières Normes canadiennes d'information sur la durabilité (NCID). La norme NCID 1 - Obligations générales en matière d'informations financières liées à la durabilité, et la norme NCID 2 - Informations à fournir en lien avec les changements climatiques, qui se fondent largement sur les normes IFRS S1 - Obligations générales en matière d'informations financières liées à la durabilité et IFRS S2 - Informations à fournir en lien avec les changements climatiques, reprennent les propositions énoncées dans les exposés-sondages publiés le 13 mars 2024 et incluent des allègements transitoires additionnels pour certaines exigences en matière d'informations à fournir. Les NCID s'appliqueront aux BISI à la fin de l'exercice 2026, et les mesures d'allègements transitoires entraîneront le report de plusieurs exigences jusqu'à la fin de l'exercice 2029. La présentation des informations selon les NCID se fera de façon volontaire jusqu'à ce que les ACVM la rendent obligatoire.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Le 18 décembre 2024, le Conseil canadien des normes d'information sur la durabilité (CCNID) a publié ses premières Normes canadiennes d'information sur la durabilité (NCID). La norme NCID 1 - Obligations générales en matière d'informations financières liées à la durabilité, et la norme NCID 2 - Informations à fournir en lien avec les changements climatiques, qui se fondent largement sur les normes IFRS S1 - Obligations générales en matière d'informations financières liées à la durabilité et IFRS S2 - Informations à fournir en lien avec les changements climatiques, reprennent les propositions énoncées dans les exposés-sondages publiés le 13 mars 2024 et incluent des allègements transitoires additionnels pour certaines exigences en matière d'informations à fournir. Les NCID s'appliqueront aux BISI à la fin de l'exercice 2026, et les mesures d'allègements transitoires entraîneront le report de plusieurs exigences jusqu'à la fin de l'exercice 2029. La présentation des informations selon les NCID se fera de façon volontaire jusqu'à ce que les ACVM la rendent obligatoire. Le 23 avril 2025, les ACVM ont annoncé la suspension de leurs travaux sur les projets concernant la communication obligatoire d'information liée au changement climatique et les modifications des obligations d'information existantes sur la diversité. Les ACVM suivront l'évolution de la réglementation et revisiteront ces deux projets au cours des prochaines années.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Les ACVM ont suspendu leurs travaux sur la communication obligatoire liée au changement climatique et la diversité. Ce changement est substantiel car il affecte les obligations de divulgation réglementaire des banques, ce qui peut avoir des implications sur la transparence et la gestion des risques climatiques. Cela nécessite une escalade pour évaluer l'impact potentiel sur les pratiques de divulgation et de conformité de la banque
+Suspension des travaux sur la communication obligatoire, impactant potentiellement la transparence et la gestion des risques climatiques</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -787,34 +804,27 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
+          <t>Exigences de communication publique pour les banques d'importance systémique mondiale</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de 7,5 G$ pour s'établir à 148,5 G$ au 31 janvier 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de la croissance organique de l'actif pondéré en fonction des risques, de la variation du taux de change et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de 41,8 G$ pour s'établir à 182,8 G$ au 30 avril 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de l'inclusion de CWB, ainsi que de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
-        </is>
-      </c>
+          <t>Le CBCB a développé une méthodologie d'évaluation et d'exigence de capacité additionnelle d'absorption des pertes ainsi que des indicateurs utilisés par le CBCB et le Conseil de stabilité financière pour évaluer les banques d'importance systémique mondiale (BISM). Des exigences de communication publique annuelles s'appliquent aux grandes banques actives à l'échelle mondiale.
+La dernière version du préavis du BSIF intitulé Banques d'importance systémique mondiale - Obligations redditionnelles à l'égard de la mise en œuvre des exigences de communication publique pour les BISM au Canada est entrée en vigueur en 2022. Les banques canadiennes, y compris la Banque, qui n'ont pas été désignées BISM et qui ont une exposition totale (telle que calculée par le ratio de levier selon Bâle III) supérieure à l'équivalent de 200 milliards d'euros à la fin de l'exercice sont tenues de publier annuellement les indicateurs. Les indicateurs sont calculés et présentés selon des lignes directrices précises publiées par le CBCB, qui sont mises à jour chaque année. Ainsi, les valeurs obtenues ne sont peut-être pas comparables aux autres mesures présentées dans ce rapport. Le tableau suivant présente les indicateurs utilisés dans la méthode d'évaluation du CBCB permettant d'évaluer les BISM.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Non</t>
@@ -822,8 +832,8 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de G$ pour s'établir à G$ au avril, principalement en raison de l'inclusion de CWB. Ce changement est substantiel car il représente une augmentation significative du risque de crédit et de marché. Cela nécessite une surveillance accrue des expositions au risque et des impacts sur les ratios de capital
-Augmentation significative de l'actif pondéré en fonction des risques, impactant le risque de crédit et de marché</t>
+          <t>La sous section sur les exigences de communication publique pour les banques d'importance systémique mondiale a été supprimée. Ce changement est substantiel car il affecte la transparence et la conformité aux exigences de communication réglementaire. Cela nécessite une escalade pour s'assurer que la banque respecte toujours les obligations de communication
+Suppression d'informations réglementaires critiques avec des implications sur la conformité</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr"/>
@@ -836,17 +846,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
+          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -856,12 +866,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,6 %, à 15,5 % et à 17,1 % au 31 janvier 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Le ratio des fonds propres CET1 et le ratio des fonds propres de catégorie 1 sont en baisse comparativement au 31 octobre 2024, alors que le ratio du total des fonds propres est légèrement en hausse. La croissance organique de l'actif pondéré en fonction des risques a eu un impact défavorable sur les ratios, atténué par le résultat net, déduction faite des dividendes. Le rachat d'actions privilégiées pour un montant de 300 M$ effectué le 17 février 2025, déjà exclu du calcul des ratios des fonds propres au 31 janvier 2025, a eu un impact défavorable sur le ratio des fonds propres de catégorie 1, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025, a eu un impact favorable sur le ratio du total des fonds propres.</t>
+          <t>L'actif pondéré en fonction des risques a augmenté de 7,5 G$ pour s'établir à 148,5 G$ au 31 janvier 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de la croissance organique de l'actif pondéré en fonction des risques, de la variation du taux de change et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,4 %, à 15,1 % et à 16,9 % au 30 avril 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Tous les ratios des fonds propres sont en baisse comparativement au 31 octobre 2024. La croissance de l'actif pondéré en fonction des risques, principalement due à l'inclusion de CWB, a eu un impact défavorable sur les ratios, un impact atténué par les actions ordinaires émises dans le cadre de l'acquisition de CWB et par le résultat net, déduction faite des dividendes. De plus, le rachat d'actions privilégiées effectué le 17 février 2025 atténué par l'échange des actions privilégiées de CWB contre des actions privilégiées de la Banque le 20 février 2025 a eu un impact défavorable sur les ratios des fonds propres de catégorie 1 et du total des fonds propres, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025 et les obligations liées aux dettes subordonnées de CWB de 525 M$ ont eu un impact favorable sur le ratio du total des fonds propres.</t>
+          <t>L'actif pondéré en fonction des risques a augmenté de 41,8 G$ pour s'établir à 182,8 G$ au 30 avril 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de l'inclusion de CWB, ainsi que de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -871,8 +881,8 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Les ratios des fonds propres ont diminué davantage en avril, principalement en raison de l'inclusion de CWB. Ce changement est substantiel car il affecte la solidité financière de la banque et sa capacité à absorber les pertes. Cela nécessite une surveillance accrue des ratios de capital et des stratégies de gestion du capital
-Diminution des ratios de fonds propres, impactant la solidité financière et la capacité d'absorption des pertes</t>
+          <t>L'actif pondéré en fonction des risques a considérablement augmenté, principalement en raison de l'inclusion de CWB. Ce changement est substantiel car il affecte directement les ratios de capital et la gestion des risques de la banque. Cela nécessite une surveillance accrue pour évaluer l'impact sur la solvabilité et la stratégie de gestion des risques
+Augmentation significative de l'exposition au risque avec des implications sur les ratios de capital</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -905,68 +915,75 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,6 %, à 15,5 % et à 17,1 % au 31 janvier 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Le ratio des fonds propres CET1 et le ratio des fonds propres de catégorie 1 sont en baisse comparativement au 31 octobre 2024, alors que le ratio du total des fonds propres est légèrement en hausse. La croissance organique de l'actif pondéré en fonction des risques a eu un impact défavorable sur les ratios, atténué par le résultat net, déduction faite des dividendes. Le rachat d'actions privilégiées pour un montant de 300 M$ effectué le 17 février 2025, déjà exclu du calcul des ratios des fonds propres au 31 janvier 2025, a eu un impact défavorable sur le ratio des fonds propres de catégorie 1, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025, a eu un impact favorable sur le ratio du total des fonds propres.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,4 %, à 15,1 % et à 16,9 % au 30 avril 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Tous les ratios des fonds propres sont en baisse comparativement au 31 octobre 2024. La croissance de l'actif pondéré en fonction des risques, principalement due à l'inclusion de CWB, a eu un impact défavorable sur les ratios, un impact atténué par les actions ordinaires émises dans le cadre de l'acquisition de CWB et par le résultat net, déduction faite des dividendes. De plus, le rachat d'actions privilégiées effectué le 17 février 2025 atténué par l'échange des actions privilégiées de CWB contre des actions privilégiées de la Banque le 20 février 2025 a eu un impact défavorable sur les ratios des fonds propres de catégorie 1 et du total des fonds propres, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025 et les obligations liées aux dettes subordonnées de CWB de 525 M$ ont eu un impact favorable sur le ratio du total des fonds propres.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Les ratios des fonds propres ont diminué, principalement en raison de l'inclusion de CWB. Ce changement est substantiel car il affecte la capacité de la banque à respecter les des exigences prudentielles en matière de capital. Cela nécessite une surveillance accrue pour s'assurer que la banque maintient des niveaux de capital adéquats
+Diminution des ratios de fonds propres avec des implications sur la conformité réglementaire</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>Au 31 janvier 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 31,2 % et à 8,7 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. Le ratio TLAC est demeuré stable et l'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours du premier trimestre de 2025.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Au 30 avril 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 28,2 % et à 8,8 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. L'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours de la période. Cependant, la croissance de l'actif pondéré en fonction des risques, principalement attribuable à l'inclusion de CWB, a largement compensé ces émissions, ce qui a entraîné une diminution du ratio TLAC.</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Le ratio a diminué à en avril, principalement en raison de l'inclusion de CWB. Ce changement est substantiel car il affecte la capacité de la banque à absorber les pertes en cas de crise. Cela nécessite une surveillance accrue des stratégies de gestion du capital et des impacts sur la résilience financière
-Diminution du ratio, impactant la capacité d'absorption des pertes en cas de crise</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Exigences de communication publique pour les banques d'importance systémique mondiale</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Le CBCB a développé une méthodologie d'évaluation et d'exigence de capacité additionnelle d'absorption des pertes ainsi que des indicateurs utilisés par le CBCB et le Conseil de stabilité financière pour évaluer les banques d'importance systémique mondiale (BISM). Des exigences de communication publique annuelles s'appliquent aux grandes banques actives à l'échelle mondiale.
-La dernière version du préavis du BSIF intitulé Banques d'importance systémique mondiale - Obligations redditionnelles à l'égard de la mise en œuvre des exigences de communication publique pour les BISM au Canada est entrée en vigueur en 2022. Les banques canadiennes, y compris la Banque, qui n'ont pas été désignées BISM et qui ont une exposition totale (telle que calculée par le ratio de levier selon Bâle III) supérieure à l'équivalent de 200 milliards d'euros à la fin de l'exercice sont tenues de publier annuellement les indicateurs. Les indicateurs sont calculés et présentés selon des lignes directrices précises publiées par le CBCB, qui sont mises à jour chaque année. Ainsi, les valeurs obtenues ne sont peut-être pas comparables aux autres mesures présentées dans ce rapport. Le tableau suivant présente les indicateurs utilisés dans la méthode d'évaluation du CBCB permettant d'évaluer les BISM.</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>La sous section sur les exigences de communication publique pour les banques d'importance systémique mondiale a été supprimée. Ce changement est substantiel car il peut affecter la transparence et la conformité aux exigences de communication. Cela nécessite une vérification de la conformité réglementaire et de l'impact sur la transparence des informations fournies
-Potentiel impact sur la transparence et la conformité aux exigences de communication publique</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Le ratio a diminué, principalement en raison de l'inclusion de CWB, malgré les émissions nettes d'instruments. Ce changement est substantiel car il affecte la capacité de la banque à absorber les pertes en cas de crise. Cela nécessite une surveillance accrue pour s'assurer que la banque maintient des niveaux de adéquats
+Diminution du ratio avec des implications sur la capacité d'absorption des pertes</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1011,8 +1028,8 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Le nombre d'annonces de la Banque du Canada a été modifié de six à huit, et la période de baisse du taux directeur a été ajustée. Ce changement est substantiel car il reflète une révision de la politique monétaire qui peut influencer la capacité des emprunteurs à rembourser leurs dettes. Cela implique une nécessité de surveiller l'impact potentiel sur le risque de crédit de la banque
-La modification du nombre d'annonces et de la période de baisse du taux directeur peut affecter la capacité des emprunteurs à rembourser, augmentant ainsi le risque de crédit</t>
+          <t>La banque du Canada a modifié son taux directeur à huit reprises entre juin et avril, passant d'une politique de hausse à une politique de baisse. Ce changement est substantiel car il reflète une inversion de tendance dans la politique monétaire, ce qui peut avoir des implications significatives sur la capacité des emprunteurs à rembourser leurs dettes. Cela implique une surveillance accrue des risques de crédit pour la banque, notamment pour les emprunteurs à taux variable
+Inversion de tendance dans la politique monétaire, impactant potentiellement la capacité de remboursement des emprunteurs</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr"/>
@@ -1060,8 +1077,8 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>La description du contexte géopolitique et économique volatile a été supprimée. Ce changement est substantiel car il omet des facteurs externes qui influencent le risque de marché. Cela implique que la banque pourrait sous estimer les risques liés aux événements géopolitiques et économiques
-La suppression de la description du contexte géopolitique et économique pourrait conduire à une sous estimation du risque de marché</t>
+          <t>La description du contexte géopolitique et économique volatile a été supprimée. Ce changement est substantiel car il omet des facteurs externes qui influencent le risque de marché auquel la banque est exposée. Cela implique que la banque pourrait sous estimer les risques liés aux événements géopolitiques et économiques dans ses évaluations de risque
+Omission de facteurs externes influençant le risque de marché, potentiellement sous estimant les risques</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
@@ -1109,8 +1126,8 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>La mesure de risque de marché est passée d'une augmentation à une stabilité entre les trimestres. Ce changement est substantiel car il indique une inversion de tendance dans l'évaluation du risque de marché. Cela implique que la banque doit réévaluer ses stratégies de gestion du risque de marché
-L'inversion de tendance de la mesure de risque de marché nécessite une réévaluation des stratégies de gestion du risque</t>
+          <t>La mesure de risque de marché totale est passée d'une augmentation à une stabilité entre les trimestres. Ce changement est substantiel car il indique une modification dans la volatilité des portefeuilles de négociation, ce qui peut affecter la gestion des risques de marché. Cela nécessite une réévaluation des stratégies de gestion des risques pour s'assurer que la stabilité observée est durable
+Changement de la volatilité des portefeuilles de négociation, affectant potentiellement la gestion des risques de marché</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr"/>
@@ -1158,8 +1175,8 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>La date de fin du trimestre et le ratio de liquidité à court terme ont été mis à jour. Ce changement est substantiel car il reflète une amélioration de la position de liquidité de la banque. Cela implique que la banque doit confirmer la durabilité de cette amélioration dans ses rapports futurs
-L'amélioration du ratio de liquidité à court terme indique une meilleure position de liquidité, nécessitant une confirmation de sa durabilité</t>
+          <t>Le ratio de liquidité à court terme de la banque a augmenté de à entre les trimestres. Ce changement est substantiel car il montre une amélioration significative de la position de liquidité de la banque, dépassant largement les des exigences prudentielles. Cela implique que la banque est mieux préparée à faire face à des sorties de trésorerie imprévues, mais nécessite une confirmation pour s'assurer que cette amélioration est soutenable
+Amélioration significative de la position de liquidité, dépassant les des exigences prudentielles</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
@@ -1207,8 +1224,8 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>La date de référence et le pourcentage du ratio de liquidité à long terme ont été mis à jour. Ce changement est substantiel car il montre une amélioration de la position de liquidité à long terme de la banque. Cela implique que la banque doit confirmer la stabilité de cette amélioration dans ses futurs rapports
-L'amélioration du ratio de liquidité à long terme indique une meilleure position de liquidité, nécessitant une confirmation de sa stabilité</t>
+          <t>Le ratio de liquidité à long terme de la banque a augmenté de à entre les trimestres. Ce changement est substantiel car il indique une amélioration de la capacité de la banque à maintenir une liquidité stable à long terme, dépassant les des exigences prudentielles. Cela nécessite une confirmation pour s'assurer que cette amélioration est durable et alignée avec les stratégies de gestion de la liquidité
+Amélioration de la capacité de maintenir une liquidité stable à long terme, dépassant les des exigences prudentielles</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
@@ -1256,8 +1273,8 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>La mention de l'exclusion des instruments du calcul des ratios de fonds propres a été supprimée. Ce changement est substantiel car il peut affecter la transparence et la compréhension des calculs de capital. Cela implique de confirmer que les ratios de fonds propres sont correctement calculés et présentés
-Potentiel impact sur la transparence des calculs de ratios de fonds propres</t>
+          <t>La mention de l'exclusion des instruments du calcul des ratios de fonds propres a été supprimée. Ce changement est substantiel car il peut affecter la transparence et la compréhension des calculs de capital. Cela nécessite une confirmation pour s'assurer que les ratios de capital sont correctement calculés et présentés
+Potentiel impact sur la transparence des calculs de ratios de capital</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
@@ -1305,8 +1322,8 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>La date de déclaration des dividendes a changé, et le montant du dividende par action ordinaire a augmenté de cents. Ce changement est substantiel car il affecte la distribution des bénéfices et la perception des investisseurs. Cela implique de confirmer l'impact sur les flux de trésorerie et la perception du marché
-Augmentation des dividendes par action, impactant les flux de trésorerie et la perception des investisseurs</t>
+          <t>La date de déclaration des dividendes a changé et le montant du dividende par action ordinaire a augmenté. Ce changement est substantiel car il affecte la distribution des bénéfices et peut influencer la perception des investisseurs. Cela nécessite une confirmation pour s'assurer que les distributions sont correctement alignées avec les politiques de la banque
+Changement dans la distribution des bénéfices avec un impact potentiel sur la perception des investisseurs</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
@@ -1354,8 +1371,8 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Les débentures subordonnées ont été ajoutées à la liste des instruments de fonds propres convertibles en cas de déclenchement des clauses FPUNV. Ce changement est substantiel car il modifie le potentiel de conversion des instruments de capital. Cela nécessite une évaluation de l'impact sur la structure de capital et la gestion des risques
-Modification du potentiel de conversion des instruments de capital, impactant la gestion des risques</t>
+          <t>Les instruments de fonds propres convertibles ont été modifiés avec l'ajout des débentures subordonnées. Ce changement est substantiel car il affecte la structure de conversion en cas de déclenchement des clauses FPUNV. Cela nécessite une évaluation de l'impact sur la gestion des risques et la planification de la recapitalisation
+Modification des instruments de conversion avec des implications sur la gestion des risques</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
@@ -1403,8 +1420,8 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Les chiffres de conversion maximale et de l'effet dilutif ont été mis à jour, ainsi que la date de référence. Ce changement est substantiel car il affecte la perception du risque de dilution pour les actionnaires. Cela implique de confirmer l'exactitude des calculs et l'impact potentiel sur les actionnaires
-Mise à jour des chiffres de conversion et de l'effet dilutif, impactant la perception du risque de dilution</t>
+          <t>Le nombre maximum d'actions ordinaires convertibles et l'effet dilutif ont été mis à jour. Ce changement est substantiel car il modifie le potentiel de dilution en cas de conversion des instruments de fonds propres. Cela nécessite une évaluation pour comprendre l'impact sur les actionnaires et la structure du capital
+Changement dans le potentiel de dilution des actions ordinaires en cas de conversion</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
@@ -1452,8 +1469,8 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Le ratio de levier a augmenté à en avril, principalement en raison de l'acquisition de CWB. Ce changement est substantiel car il reflète une amélioration de la capacité de la banque à supporter ses actifs avec ses fonds propres. Cela nécessite une évaluation de l'impact sur la gestion des risques et la conformité réglementaire
-Augmentation du ratio de levier, reflétant une amélioration de la capacité à supporter les actifs avec les fonds propres</t>
+          <t>Le ratio de levier a augmenté, principalement en raison de l'acquisition de CWB. Ce changement est substantiel car il affecte la capacité de la banque à gérer son levier financier. Cela nécessite une évaluation pour comprendre l'impact sur la gestion du capital et la stratégie de croissance
+Augmentation du ratio de levier avec des implications sur la gestion du capital</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
@@ -1493,7 +1510,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>La mention des actions privilégiées série rachetées a été supprimée. Ce changement est substantiel car il peut affecter la transparence des informations sur les rachats d'actions. Cela implique de confirmer que les informations sur les rachats sont correctement présentées et comprises
+          <t>La mention des actions privilégiées série rachetées a été supprimée. Ce changement est substantiel car il peut affecter la transparence des informations sur les rachats d'actions. Cela nécessite une confirmation pour s'assurer que les informations sur les rachats sont correctement communiquées
 Potentiel impact sur la transparence des informations sur les rachats d'actions</t>
         </is>
       </c>
@@ -1502,442 +1519,447 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Au 21 février 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 216 059 et le nombre d'options en cours est de 11 778 661.</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Au 23 mai 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 340 763 et le nombre d'options en cours est de 11 619 774.</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Les chiffres des actions ordinaires et des options en circulation ont été mis à jour. Ce changement est mineur car il reflète des ajustements normaux dans le cadre des opérations courantes. Cela implique de tenir à jour les registres pour assurer une information précise aux investisseurs
+Mise à jour des chiffres de capital en circulation sans impact significatif</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Exposition maximale au risque de crédit selon les catégories d'actifs de Bâle (1)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Premier trimestre 2025 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Premier trimestre 2025 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Deuxième trimestre 2025 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Deuxième trimestre 2025 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>Au 31 janvier 2025, les actifs liquides de niveau 1 représentent 84 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Au 30 avril 2025, les actifs liquides de niveau 1 représentent 84 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 31 janvier 2025 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 30 avril 2025 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 31 janvier 2025, ainsi que les données comparatives au 31 octobre 2024. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 30 avril 2025, ainsi que les données comparatives au 31 octobre 2024. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de ses clients représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de sa clientèle représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Divulgation d'information sur les risques</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Le Rapport annuel 2024, le Rapport aux actionnaires - Premier trimestre 2025 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Le Rapport annuel 2024, le Rapport aux actionnaires - Deuxième trimestre 2025 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Accord de Bâle</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>La ligne directrice Capacité totale d'absorption des pertes (Total Loss Absorbing Capacity ou TLAC) du BSIF, qui s'applique à toutes les BISI dans le cadre des règlements sur la recapitalisation interne du gouvernement fédéral, vise à faire en sorte qu'une BISI dispose d'une capacité d'absorption des pertes suffisante pour soutenir sa recapitalisation interne dans le cas peu probable où elle deviendrait non viable. La TLAC disponible comprend le total des fonds propres ainsi que certaines dettes de premier rang non garanties qui satisfont tous les critères d'admissibilité à la ligne directrice TLAC du BSIF. Le BSIF exige des BISI qu'elles maintiennent un ratio TLAC fondé sur les risques d'au moins 25,0 % (incluant la RSI) de l'actif pondéré en fonction des risques et un ratio de levier TLAC d'au moins 7,25 %. Le ratio TLAC se calcule en divisant la TLAC disponible par l'actif pondéré en fonction des risques et le ratio de levier TLAC se calcule en divisant la TLAC disponible par l'exposition totale. Au 31 janvier 2025, la valeur des éléments de passif en circulation faisant l'objet de règlements sur la conversion aux fins de la recapitalisation interne s'élève à 23,8 G$ (23,5 G$ au 31 octobre 2024).</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>La ligne directrice Capacité totale d'absorption des pertes (Total Loss Absorbing Capacity ou TLAC) du BSIF, qui s'applique à toutes les BISI dans le cadre des règlements sur la recapitalisation interne du gouvernement fédéral, vise à faire en sorte qu'une BISI dispose d'une capacité d'absorption des pertes suffisante pour soutenir sa recapitalisation interne dans le cas peu probable où elle deviendrait non viable. La TLAC disponible comprend le total des fonds propres ainsi que certaines dettes de premier rang non garanties qui satisfont tous les critères d'admissibilité à la ligne directrice TLAC du BSIF. Le BSIF exige des BISI qu'elles maintiennent un ratio TLAC fondé sur les risques d'au moins 25,0 % (incluant la RSI) de l'actif pondéré en fonction des risques et un ratio de levier TLAC d'au moins 7,25 %. Le ratio TLAC se calcule en divisant la TLAC disponible par l'actif pondéré en fonction des risques et le ratio de levier TLAC se calcule en divisant la TLAC disponible par l'exposition totale. Au 30 avril 2025, la valeur des éléments de passif en circulation faisant l'objet de règlements sur la conversion aux fins de la recapitalisation interne s'élève à 23,4 G$ (23,5 G$ au 31 octobre 2024).</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Au 21 février 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 216 059 et le nombre d'options en cours est de 11 778 661.</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Au 23 mai 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 340 763 et le nombre d'options en cours est de 11 619 774.</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Variation de l'actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>La rubrique « Mises à jour des modèles » inclut la mise en œuvre des modèles, les changements à l'étendue des modèles ou tout autre changement visant à régler les dysfonctionnements liés aux modèles.</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>La rubrique « Mises à jour des modèles » inclut la mise en œuvre des nouveaux modèles, les changements à l'étendue des modèles ou tout autre changement visant à régler les dysfonctionnements liés aux modèles.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Variation de l'actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>La rubrique « Mises à jour des modèles » inclut la mise en œuvre des modèles, les changements à l'étendue des modèles ou tout autre changement visant à régler les dysfonctionnements liés aux modèles.</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>La rubrique « Mises à jour des modèles » inclut la mise en œuvre des nouveaux modèles, les changements à l'étendue des modèles ou tout autre changement visant à régler les dysfonctionnements liés aux modèles.</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Au cours du trimestre terminé le 31 janvier 2025, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Au cours du trimestre et du semestre terminés le 30 avril 2025, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr"/>
+      <c r="J32" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J32"/>

--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/text_comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/text_comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analyse complète" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analyse complète'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analyse complète'!$A$1:$J$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEBD0"/>
+        <bgColor rgb="00FDEBD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,12 +78,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -448,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -550,7 +559,11 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>OUI — l'ajout de la mise à jour de la ligne directrice B-15 sur la gestion des risques climatiques, incluant le report de l'exigence de divulgation des émissions de GES de portée trois, constitue une nouvelle mention réglementaire. Ce changement affecte les thèmes AMF ESG_CLIMATIQUE et NOUVELLE_MENTION_REGLEMENTAIRE. L'analyste doit suivre l'impact de cette mise à jour sur les pratiques de divulgation de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Risque climatique, ESG, nouvelle mention réglementaire, information ajoutée.
+Ce qui change : Le T2 ajoute une mise à jour de la ligne directrice B-15 par le BSIF sur la gestion des risques climatiques, incluant le report de l'exigence de divulgation des émissions de GES de portée trois, qui n'était pas mentionnée au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -598,7 +611,11 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>OUI — l'ajout d'informations sur la suspension par les ACVM des projets concernant la communication obligatoire d'information liée au changement climatique et la diversité constitue une nouvelle mention réglementaire. Ce changement affecte les thèmes AMF ESG_CLIMATIQUE et NOUVELLE_MENTION_REGLEMENTAIRE. L'analyste doit suivre l'impact de cette suspension sur les pratiques de divulgation de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Risque climatique, ESG, nouvelle mention réglementaire, information ajoutée.
+Ce qui change : Le T2 ajoute des informations sur la suspension par les ACVM des projets concernant la communication obligatoire d'information liée au changement climatique et la diversité, qui n'étaient pas mentionnées au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -639,10 +656,18 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>OUI — la suppression de la sous-section sur les exigences de communication publique pour les banques d'importance systémique mondiale est une modification significative au t2. Ce retrait impacte directement les exigences réglementaires, ce qui est pertinent pour les thèmes AMF DIVULGATION_RETRAIT et EXIGENCES_REGLEMENTAIRES. La surveillance doit intégrer cette modification dans l'analyse des obligations de communication réglementaire.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information retirée, exigences réglementaires ou conformité.
+Ce qui change : Le T2 retire une sous-section entière sur les exigences de communication publique pour les banques d'importance systémique mondiale, qui était présente au T1.
+Pertinence métier : Ce changement met l'accent sur la transparence de la divulgation concernant les obligations de communication de la banque. Le retrait de cette information peut influencer la perception de la conformité de la banque aux exigences réglementaires et sa comparabilité avec les pairs.
+Point de surveillance : Exigences réglementaires — Le changement indique une modification de la divulgation sur les obligations de communication, ce qui peut affecter la comparabilité avec les pairs et la lecture des pratiques de conformité.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Oui c'est un vrai changment</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -687,7 +712,11 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>OUI — la suppression de la description du contexte géopolitique et économique volatile au t2, qui était présente au t1, constitue un retrait significatif de divulgation. Ce changement affecte la transparence sur les risques de marché, touchant les thèmes AMF MODIFICATION_TEXTE_RISQUE et DIVULGATION_RETRAIT. L'analyste doit surveiller l'impact de ce retrait sur la perception des risques par les investisseurs.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, information retirée.
+Ce qui change : Le T2 retire la description du contexte géopolitique et économique volatile, incluant les mesures commerciales, la guerre russo-ukrainienne, et les affrontements entre Israël et le Hamas, qui étaient mentionnés au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -727,7 +756,11 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>OUI — l'ajout de la sous-section sur les revenus de négociation et de souscription quotidiens constitue une nouvelle divulgation. Ce changement affecte les thèmes AMF DIVULGATION_AJOUT et MODIFICATION_TEXTE_RISQUE. L'analyste doit suivre l'impact de cette nouvelle divulgation sur la perception des risques de marché par les investisseurs.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information ajoutée, texte de risque modifié.
+Ce qui change : Le T2 ajoute une sous-section sur les revenus de négociation et de souscription quotidiens, qui n'était pas présente au T1. Cette nouvelle divulgation inclut des détails sur les performances de marché et les pertes nettes de négociation.
+Pertinence métier : Ce changement met l'accent sur la transparence accrue de la banque concernant ses performances de marché. L'ajout de cette sous-section permet une meilleure compréhension des risques associés aux activités de négociation et de souscription, ce qui peut influencer la perception des investisseurs et des régulateurs sur la gestion des risques de la banque.
+Point de surveillance : Revenus de négociation — Le changement indique que la banque fournit plus de détails sur ses performances de marché. Ce point permet de suivre la transparence de la banque sur ses activités de négociation et la comparabilité de sa divulgation avec les autres institutions.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -740,24 +773,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Activités de gestion</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
+          <t>Variation de l'actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>La rubrique « Mises à jour des modèles » inclut la mise en œuvre des modèles, les changements à l'étendue des modèles ou tout autre changement visant à régler les dysfonctionnements liés aux modèles.</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Le 3 février 2025, lors de la clôture de l'acquisition de CWB, la Banque a émis un total de 50 272 878 actions ordinaires, pour un produit brut de 6,3 G$.</t>
+          <t>La rubrique « Mises à jour des modèles » inclut la mise en œuvre des nouveaux modèles, les changements à l'étendue des modèles ou tout autre changement visant à régler les dysfonctionnements liés aux modèles.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -767,7 +808,11 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>OUI — l'émission de 50 272 878 actions ordinaires pour un produit brut de 6,3 G$ lors de l'acquisition de CWB est une nouvelle divulgation au t2. Cet ajout impacte directement les fonds propres réglementaires, ce qui est pertinent pour les thèmes AMF DIVULGATION_AJOUT et FONDS_PROPRES_REGLEMENTAIRES. La surveillance doit intégrer cette augmentation des fonds propres dans l'analyse des ratios réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, méthode de calcul ou approche modifiée.
+Ce qui change : Le T2 précise que les modèles mis en œuvre sont 'nouveaux', ce qui n'était pas mentionné au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution de l'approche de gestion des risques de la banque. L'ajout de cette précision modifie la perception de la solidité des modèles de risque de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Méthodologie de gestion des risques — Le changement indique une modification de l'approche de gestion des risques, ce qui peut affecter la comparabilité avec les pairs et la lecture des pratiques de gestion des risques.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -797,7 +842,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Le 3 février 2025, dans le cadre de l'acquisition de CWB, la Banque a acquis les obligations liées aux dettes subordonnées de CWB pour un montant total de 525 M$, qui incluait une débenture de 125 M$ portant intérêt à 4,840 % et échéant le 29 juin 2030 (le 2 mai 2025, la Banque a informé les détenteurs de son intention de racheter les débentures le 29 juin 2025, à un prix de rachat égal au capital impayé plus l'intérêt couru et impayé), une débenture de 150 M$ portant intérêt à 5,937 % et échéant le 22 décembre 2032 et une débenture de 250 M$ portant intérêt à 5,949 % et échéant le 29 janvier 2034. Comme les débentures respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
+          <t>Le 20 février 2025, il y a eu un échange de la totalité des actions privilégiées de premier rang, série 5 et série 9, émises et en circulation de CWB, contre des actions privilégiées de premier rang essentiellement équivalentes de la Banque Nationale, série 47 et série 49, donnant droit à un dividende non cumulatif à taux rajusté tous les cinq ans, portant intérêt à 6,371 % et 7,651 %. La Banque a échangé 10 000 000 actions privilégiées pour un montant total de 264 M$. Comme les actions privilégiées, série 47 et série 49, respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -807,7 +852,11 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>OUI — l'acquisition des obligations liées aux dettes subordonnées de CWB pour un montant total de 525 M$ est une nouvelle divulgation au t2. Cet ajout impacte directement les fonds propres réglementaires, ce qui est pertinent pour les thèmes AMF DIVULGATION_AJOUT et FONDS_PROPRES_REGLEMENTAIRES. La surveillance doit intégrer cette acquisition dans l'analyse des ratios réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information ajoutée, fonds propres réglementaires.
+Ce qui change : Le T2 ajoute des informations sur l'échange de la totalité des actions privilégiées de premier rang de CWB contre des actions privilégiées de la Banque Nationale.
+Pertinence métier : Ce changement met l'accent sur l'évolution de la structure de capital de la banque suite à une acquisition majeure. L'échange d'actions privilégiées modifie la composition des fonds propres réglementaires et peut influencer la perception de la solidité financière de la banque par les régulateurs et les investisseurs.
+Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la composition des fonds propres, ce qui peut affecter les ratios de capital et la comparabilité avec les pairs.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -823,7 +872,11 @@
           <t>Activités de gestion</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -831,13 +884,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Le 17 février 2025, soit le premier jour ouvrable suivant la date de rachat du 15 février 2025, la Banque a terminé le rachat de la totalité des actions privilégiées de premier rang à dividende non cumulatif à taux rajusté tous les cinq ans, série 32, émises et en circulation. Tel que prévu dans les conditions relatives aux actions, le prix de rachat était de 25,00 $ l'action, plus les dividendes périodiques déclarés et impayés. La Banque a racheté 12 000 000 actions privilégiées série 32 pour un prix total de 300 M$. Ces instruments ont été exclus du calcul des ratios de fonds propres au 31 janvier 2025.</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Le 20 février 2025, il y a eu un échange de la totalité des actions privilégiées de premier rang, série 5 et série 9, émises et en circulation de CWB, contre des actions privilégiées de premier rang essentiellement équivalentes de la Banque Nationale, série 47 et série 49, donnant droit à un dividende non cumulatif à taux rajusté tous les cinq ans, portant intérêt à 6,371 % et 7,651 %. La Banque a échangé 10 000 000 actions privilégiées pour un montant total de 264 M$. Comme les actions privilégiées, série 47 et série 49, respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
+          <t>Le 17 février 2025, soit le premier jour ouvrable suivant la date de rachat du 15 février 2025, la Banque a terminé le rachat de la totalité des actions privilégiées de premier rang à dividende non cumulatif à taux rajusté tous les cinq ans, série 32, émises et en circulation. Tel que prévu dans les conditions relatives aux actions, le prix de rachat était de 25,00 $ l'action, plus les dividendes périodiques déclarés et impayés. La Banque a racheté 12 000 000 actions privilégiées série 32 pour un prix total de 300 M$.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -847,10 +904,18 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>OUI — l'échange de la totalité des actions privilégiées de premier rang de CWB contre celles de la Banque Nationale est une nouvelle divulgation au t2. Cet ajout impacte directement les fonds propres réglementaires, ce qui est pertinent pour les thèmes AMF DIVULGATION_AJOUT et FONDS_PROPRES_REGLEMENTAIRES. La surveillance doit intégrer cet échange dans l'analyse des ratios réglementaires.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information retirée, fonds propres réglementaires.
+Ce qui change : Le T2 retire la mention de l'exclusion des instruments du calcul des ratios de fonds propres au 31 janvier, qui était présente au T1.
+Pertinence métier : Ce changement met l'accent sur la transparence de la divulgation concernant les fonds propres réglementaires. Le retrait de cette information peut influencer la perception de la solidité financière de la banque et sa conformité aux exigences réglementaires.
+Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la divulgation sur la composition des fonds propres, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Non pas un vrai changement</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -860,17 +925,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Activités de gestion</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -880,12 +945,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Le 17 février 2025, soit le premier jour ouvrable suivant la date de rachat du 15 février 2025, la Banque a terminé le rachat de la totalité des actions privilégiées de premier rang à dividende non cumulatif à taux rajusté tous les cinq ans, série 32, émises et en circulation. Tel que prévu dans les conditions relatives aux actions, le prix de rachat était de 25,00 $ l'action, plus les dividendes périodiques déclarés et impayés. La Banque a racheté 12 000 000 actions privilégiées série 32 pour un prix total de 300 M$. Ces instruments ont été exclus du calcul des ratios de fonds propres au 31 janvier 2025.</t>
+          <t>Si un événement déclencheur faisant intervenir les clauses FPUNV devait se produire, toutes les actions privilégiées et les BCRL de la Banque ainsi que les billets à moyen terme échéant le 16 août 2032, le 15 février 2034 et le 15 février 2035, qui sont des instruments de fonds propres assortis d'une clause FPUNV, seraient convertis en actions ordinaires de la Banque selon une formule de conversion automatique, à un prix de conversion correspondant au plus élevé des montants suivants : i) un prix plancher contractuel de 5,00 $; ii) le cours du marché des actions ordinaires de la Banque à la date de l'événement déclencheur (cours moyen pondéré sur 10 jours).</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Le 17 février 2025, soit le premier jour ouvrable suivant la date de rachat du 15 février 2025, la Banque a terminé le rachat de la totalité des actions privilégiées de premier rang à dividende non cumulatif à taux rajusté tous les cinq ans, série 32, émises et en circulation. Tel que prévu dans les conditions relatives aux actions, le prix de rachat était de 25,00 $ l'action, plus les dividendes périodiques déclarés et impayés. La Banque a racheté 12 000 000 actions privilégiées série 32 pour un prix total de 300 M$.</t>
+          <t>Si un événement déclencheur faisant intervenir les clauses FPUNV devait se produire, toutes les actions privilégiées et les BCRL de la Banque ainsi que les billets à moyen terme et les débentures subordonnées, qui sont des instruments de fonds propres assortis d'une clause FPUNV, seraient convertis en actions ordinaires de la Banque selon une formule de conversion automatique, à un prix de conversion correspondant au plus élevé des montants suivants : i) un prix plancher contractuel de 5,00 $; ii) le cours du marché des actions ordinaires de la Banque à la date de l'événement déclencheur (cours moyen pondéré sur 10 jours).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -895,7 +960,11 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>OUI — la suppression de la mention de l'exclusion des instruments du calcul des ratios de fonds propres au 31 janvier 2025 est une modification significative au t2. Ce retrait impacte directement les fonds propres réglementaires, ce qui est pertinent pour les thèmes AMF DIVULGATION_RETRAIT et FONDS_PROPRES_REGLEMENTAIRES. La surveillance doit intégrer cette modification dans l'analyse des ratios réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information ajoutée, fonds propres réglementaires.
+Ce qui change : Le T2 ajoute les débentures subordonnées à la liste des instruments convertibles en actions ordinaires en cas de déclenchement des clauses FPUNV.
+Pertinence métier : Ce changement met l'accent sur la transparence de la divulgation concernant les fonds propres réglementaires. L'ajout de ces débentures modifie la perception de la solidité financière de la banque et sa capacité à absorber les pertes en cas de crise.
+Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la composition des instruments convertibles, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -908,17 +977,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
+          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -928,12 +997,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Si un événement déclencheur faisant intervenir les clauses FPUNV devait se produire, toutes les actions privilégiées et les BCRL de la Banque ainsi que les billets à moyen terme échéant le 16 août 2032, le 15 février 2034 et le 15 février 2035, qui sont des instruments de fonds propres assortis d'une clause FPUNV, seraient convertis en actions ordinaires de la Banque selon une formule de conversion automatique, à un prix de conversion correspondant au plus élevé des montants suivants : i) un prix plancher contractuel de 5,00 $; ii) le cours du marché des actions ordinaires de la Banque à la date de l'événement déclencheur (cours moyen pondéré sur 10 jours).</t>
+          <t>L'actif pondéré en fonction des risques a augmenté de 7,5 G$ pour s'établir à 148,5 G$ au 31 janvier 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de la croissance organique de l'actif pondéré en fonction des risques, de la variation du taux de change et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Si un événement déclencheur faisant intervenir les clauses FPUNV devait se produire, toutes les actions privilégiées et les BCRL de la Banque ainsi que les billets à moyen terme et les débentures subordonnées, qui sont des instruments de fonds propres assortis d'une clause FPUNV, seraient convertis en actions ordinaires de la Banque selon une formule de conversion automatique, à un prix de conversion correspondant au plus élevé des montants suivants : i) un prix plancher contractuel de 5,00 $; ii) le cours du marché des actions ordinaires de la Banque à la date de l'événement déclencheur (cours moyen pondéré sur 10 jours).</t>
+          <t>L'actif pondéré en fonction des risques a augmenté de 41,8 G$ pour s'établir à 182,8 G$ au 30 avril 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de l'inclusion de CWB, ainsi que de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,7 +1012,11 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>OUI — l'ajout des débentures subordonnées dans la liste des instruments convertibles en cas de déclenchement des clauses FPUNV est une nouvelle divulgation au t2. Cet ajout impacte directement les fonds propres réglementaires, ce qui est pertinent pour les thèmes AMF FONDS_PROPRES_REGLEMENTAIRES et DIVULGATION_AJOUT. La surveillance doit intégrer cet ajout dans l'analyse des fonds propres réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, fonds propres réglementaires.
+Ce qui change : Le T2 ajoute l'inclusion de CWB comme facteur d'augmentation de l'actif pondéré en fonction des risques, absent au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Fonds propres réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -976,12 +1049,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,6 %, à 15,5 % et à 17,1 % au 31 janvier 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Le ratio des fonds propres CET1 et le ratio des fonds propres de catégorie 1 sont en baisse comparativement au 31 octobre 2024, alors que le ratio du total des fonds propres est légèrement en hausse. La croissance organique de l'actif pondéré en fonction des risques a eu un impact défavorable sur les ratios, atténué par le résultat net, déduction faite des dividendes. Le rachat d'actions privilégiées pour un montant de 300 M$ effectué le 17 février 2025, déjà exclu du calcul des ratios des fonds propres au 31 janvier 2025, a eu un impact défavorable sur le ratio des fonds propres de catégorie 1, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025, a eu un impact favorable sur le ratio du total des fonds propres.</t>
+          <t>Le ratio de levier en date du 31 janvier 2025 s'établit à 4,3 %, comparativement à 4,4 % au 31 octobre 2024. La baisse du ratio de levier s'explique essentiellement par l'augmentation de l'exposition totale, en partie contrebalancée par la croissance des fonds propres de catégorie 1.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,4 %, à 15,1 % et à 16,9 % au 30 avril 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Tous les ratios des fonds propres sont en baisse comparativement au 31 octobre 2024. La croissance de l'actif pondéré en fonction des risques, principalement due à l'inclusion de CWB, a eu un impact défavorable sur les ratios, un impact atténué par les actions ordinaires émises dans le cadre de l'acquisition de CWB et par le résultat net, déduction faite des dividendes. De plus, le rachat d'actions privilégiées effectué le 17 février 2025 atténué par l'échange des actions privilégiées de CWB contre des actions privilégiées de la Banque le 20 février 2025 a eu un impact défavorable sur les ratios des fonds propres de catégorie 1 et du total des fonds propres, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025 et les obligations liées aux dettes subordonnées de CWB de 525 M$ ont eu un impact favorable sur le ratio du total des fonds propres.</t>
+          <t>Le ratio de levier en date du 30 avril 2025 s'établit à 4,7 %, comparativement à 4,4 % au 31 octobre 2024. L'augmentation du ratio de levier s'explique essentiellement par la croissance des fonds propres de catégorie 1 en lien avec les actions ordinaires émises dans le cadre de l'acquisition de CWB, en partie contrebalancée par l'augmentation de l'exposition totale.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -991,7 +1064,11 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>OUI — la diminution des ratios des fonds propres, principalement due à l'inclusion de CWB, est une modification significative au t2. Ce changement impacte directement les ratios réglementaires et les fonds propres, ce qui est pertinent pour les thèmes AMF RATIOS_REGLEMENTAIRES et FONDS_PROPRES_REGLEMENTAIRES. La surveillance doit intégrer cette modification dans l'analyse des ratios réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, ratio ou seuil prudentiel.
+Ce qui change : Le T2 ajoute l'acquisition de CWB comme facteur influençant le ratio de levier, absent au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Ratios réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1024,12 +1101,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Le ratio de levier en date du 31 janvier 2025 s'établit à 4,3 %, comparativement à 4,4 % au 31 octobre 2024. La baisse du ratio de levier s'explique essentiellement par l'augmentation de l'exposition totale, en partie contrebalancée par la croissance des fonds propres de catégorie 1.</t>
+          <t>Au 31 janvier 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 31,2 % et à 8,7 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. Le ratio TLAC est demeuré stable et l'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours du premier trimestre de 2025.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Le ratio de levier en date du 30 avril 2025 s'établit à 4,7 %, comparativement à 4,4 % au 31 octobre 2024. L'augmentation du ratio de levier s'explique essentiellement par la croissance des fonds propres de catégorie 1 en lien avec les actions ordinaires émises dans le cadre de l'acquisition de CWB, en partie contrebalancée par l'augmentation de l'exposition totale.</t>
+          <t>Au 30 avril 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 28,2 % et à 8,8 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. L'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours de la période. Cependant, la croissance de l'actif pondéré en fonction des risques, principalement attribuable à l'inclusion de CWB, a largement compensé ces émissions, ce qui a entraîné une diminution du ratio TLAC.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1039,773 +1116,789 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>OUI — l'augmentation du ratio de levier, principalement due à l'acquisition de CWB, est une modification significative au t2. Ce changement impacte directement les ratios réglementaires, ce qui est pertinent pour le thème AMF RATIOS_REGLEMENTAIRES. La surveillance doit intégrer cette modification dans l'analyse des ratios réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, ratio ou seuil prudentiel.
+Ce qui change : Le T2 ajoute l'inclusion de CWB comme facteur influençant le ratio TLAC, absent au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Ratios réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Activités de gestion</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Le 3 février 2025, lors de la clôture de l'acquisition de CWB, la Banque a émis un total de 50 272 878 actions ordinaires, pour un produit brut de 6,3 G$.</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information ajoutée, capital réglementaire.
+Ce qui change : Le T2 ajoute des informations sur l'émission de 50 272 878 actions ordinaires pour un produit brut de 6,3 G$ lors de l'acquisition de CWB.
+Pertinence métier : Ce changement met l'accent sur l'évolution de la structure de capital de la banque suite à une acquisition majeure. L'émission d'actions ordinaires modifie la composition du capital réglementaire et peut influencer la perception de la solidité financière de la banque par les régulateurs et les investisseurs.
+Point de surveillance : Capital réglementaire — Le changement indique une augmentation du capital par émission d'actions, ce qui peut affecter les ratios de capital et la comparabilité avec les pairs.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>c'et pas un vrai changement pas important vraiment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Activités de gestion</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Le 3 février 2025, dans le cadre de l'acquisition de CWB, la Banque a acquis les obligations liées aux dettes subordonnées de CWB pour un montant total de 525 M$, qui incluait une débenture de 125 M$ portant intérêt à 4,840 % et échéant le 29 juin 2030 (le 2 mai 2025, la Banque a informé les détenteurs de son intention de racheter les débentures le 29 juin 2025, à un prix de rachat égal au capital impayé plus l'intérêt couru et impayé), une débenture de 150 M$ portant intérêt à 5,937 % et échéant le 22 décembre 2032 et une débenture de 250 M$ portant intérêt à 5,949 % et échéant le 29 janvier 2034. Comme les débentures respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information ajoutée, fonds propres réglementaires.
+Ce qui change : Le T2 ajoute des informations sur l'acquisition de 525 M$ d'obligations liées aux dettes subordonnées de CWB, incluant des débentures portant intérêt à des taux spécifiques.
+Pertinence métier : Ce changement met l'accent sur l'intégration de nouveaux instruments de fonds propres dans le calcul des fonds propres réglementaires. L'acquisition de ces obligations peut influencer la structure de capital de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la composition des fonds propres, ce qui peut affecter les ratios de capital et la comparabilité avec les pairs.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>oui une nouvelle idee mais vraiment pas pertinant quand meme pour nous</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Exposition maximale au risque de crédit selon les catégories d'actifs de Bâle (1)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Premier trimestre 2025 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Premier trimestre 2025 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Deuxième trimestre 2025 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Deuxième trimestre 2025 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de période de référence.
+Ce qui change : Le T2 met à jour les documents de référence pour le deuxième trimestre au lieu du premier trimestre. Ce changement est purement factuel et ne modifie pas la substance de la divulgation.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale des périodes de reporting. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>VaR des portefeuilles de négociation (1) (2)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>La moyenne de la VaR totale des portefeuilles de négociation a augmenté, passant de 7,9 M$ à 12,1 M$ entre le quatrième trimestre de 2024 et le premier trimestre de 2025, principalement en raison d'une hausse du risque de taux d'intérêt.</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>La moyenne de la VaR totale des portefeuilles de négociation est demeurée stable entre le premier trimestre et le deuxième trimestre de 2025.</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 indique que la mesure de risque de marché est restée stable entre le premier et le deuxième trimestre, contrairement à une augmentation mentionnée précédemment. Ce changement est purement factuel et ne modifie pas la substance de la divulgation.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale des mesures de risque propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Au 31 janvier 2025, les actifs liquides de niveau 1 représentent 84 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Au 30 avril 2025, les actifs liquides de niveau 1 représentent 84 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de date de référence.
+Ce qui change : Le T2 met à jour la date de référence pour les actifs liquides de niveau 1, passant de janvier à avril. Ce changement est purement factuel et ne modifie pas la substance de la divulgation.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale des dates de reporting. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour de date — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 31 janvier 2025 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 30 avril 2025 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de date de référence.
+Ce qui change : Le T2 met à jour la date de référence pour la variation des sorties de trésorerie, passant de janvier à avril. Ce changement est purement factuel et ne modifie pas la substance de la divulgation.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale des dates de reporting. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour de date — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Ratio structurel de liquidité à long terme</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 31 janvier 2025 est de 123 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 30 avril 2025 est de 127 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 met à jour la date et le pourcentage du NSFR, passant de janvier à avril et de 123 % à 127 %. Ce changement est purement factuel et ne modifie pas la substance de la divulgation.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale des mesures de liquidité propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 31 janvier 2025, ainsi que les données comparatives au 31 octobre 2024. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 30 avril 2025, ainsi que les données comparatives au 31 octobre 2024. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de date de référence.
+Ce qui change : Le T2 met à jour la date des échéances contractuelles résiduelles, passant de janvier à avril. Ce changement est purement factuel et ne modifie pas la substance de la divulgation.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de ses clients représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de sa clientèle représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Reformulation mineure.
+Ce qui change : Le T2 remplace le terme 'ses clients' par 'sa clientèle'. Ce changement est purement stylistique et ne modifie pas la substance de la divulgation.
+Pertinence métier : Cette reformulation ne constitue pas une nouvelle idée à surveiller, car elle n'apporte aucune modification de fond à la divulgation. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Reformulation mineure — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Divulgation d'information sur les risques</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Le Rapport annuel 2024, le Rapport aux actionnaires - Premier trimestre 2025 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Le Rapport annuel 2024, le Rapport aux actionnaires - Deuxième trimestre 2025 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de période de référence.
+Ce qui change : Le T2 met à jour le rapport aux actionnaires pour le deuxième trimestre au lieu du premier trimestre. Ce changement est purement factuel et ne modifie pas la substance de la divulgation.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Dividendes</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Le 25 février 2025, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,14 $ par action ordinaire, payable le 1 er mai 2025 aux actionnaires inscrits le 31 mars 2025.</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Le 27 mai 2025, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,18 $ par action ordinaire, en hausse de 4 cents ou 3,4 %, payable le 1 er août 2025 aux actionnaires inscrits le 30 juin 2025.</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 met à jour la date de déclaration des dividendes, le montant du dividende par action ordinaire, et les dates de paiement et d'inscription.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale d'un chiffre propre à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Au 21 février 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 216 059 et le nombre d'options en cours est de 11 778 661.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Au 23 mai 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 340 763 et le nombre d'options en cours est de 11 619 774.</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 met à jour les chiffres des actions ordinaires et des options en circulation, sans modification de fond.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale d'un chiffre propre à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 264 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 78,7 % selon le nombre d'actions ordinaires de la Banque en circulation au 31 janvier 2025.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 472 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 79,0 % selon le nombre d'actions ordinaires de la Banque en circulation au 30 avril 2025.</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 met à jour les chiffres de conversion maximale et de l'effet dilutif, sans modification de fond.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale d'un chiffre propre à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Au 31 janvier 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 31,2 % et à 8,7 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. Le ratio TLAC est demeuré stable et l'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours du premier trimestre de 2025.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Au 30 avril 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 28,2 % et à 8,8 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. L'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours de la période. Cependant, la croissance de l'actif pondéré en fonction des risques, principalement attribuable à l'inclusion de CWB, a largement compensé ces émissions, ce qui a entraîné une diminution du ratio TLAC.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>OUI — la diminution du ratio, principalement due à l'inclusion de CWB, est une modification significative au t2. Ce changement impacte directement les ratios réglementaires, ce qui est pertinent pour le thème AMF RATIOS_REGLEMENTAIRES. La surveillance doit intégrer cette modification dans l'analyse des ratios réglementaires.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,6 %, à 15,5 % et à 17,1 % au 31 janvier 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Le ratio des fonds propres CET1 et le ratio des fonds propres de catégorie 1 sont en baisse comparativement au 31 octobre 2024, alors que le ratio du total des fonds propres est légèrement en hausse. La croissance organique de l'actif pondéré en fonction des risques a eu un impact défavorable sur les ratios, atténué par le résultat net, déduction faite des dividendes. Le rachat d'actions privilégiées pour un montant de 300 M$ effectué le 17 février 2025, déjà exclu du calcul des ratios des fonds propres au 31 janvier 2025, a eu un impact défavorable sur le ratio des fonds propres de catégorie 1, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025, a eu un impact favorable sur le ratio du total des fonds propres.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,4 %, à 15,1 % et à 16,9 % au 30 avril 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Tous les ratios des fonds propres sont en baisse comparativement au 31 octobre 2024. La croissance de l'actif pondéré en fonction des risques, principalement due à l'inclusion de CWB, a eu un impact défavorable sur les ratios, un impact atténué par les actions ordinaires émises dans le cadre de l'acquisition de CWB et par le résultat net, déduction faite des dividendes. De plus, le rachat d'actions privilégiées effectué le 17 février 2025 atténué par l'échange des actions privilégiées de CWB contre des actions privilégiées de la Banque le 20 février 2025 a eu un impact défavorable sur les ratios des fonds propres de catégorie 1 et du total des fonds propres, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025 et les obligations liées aux dettes subordonnées de CWB de 525 M$ ont eu un impact favorable sur le ratio du total des fonds propres.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 met à jour les ratios des fonds propres, sans modification de fond.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale d'un chiffre propre à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Les actions privilégiées série 32 rachetées le 17 février 2025 pour un prix total de 300 M$ ont été exclues du calcul.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>OUI — la suppression de la mention des actions privilégiées série 32 rachetées pour un prix total de 300 M$ est une modification significative au t2. Ce retrait impacte directement les fonds propres réglementaires, ce qui est pertinent pour les thèmes AMF DIVULGATION_RETRAIT et FONDS_PROPRES_REGLEMENTAIRES. La surveillance doit intégrer cette modification dans l'analyse des ratios réglementaires.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Variation de l'actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>La rubrique « Mises à jour des modèles » inclut la mise en œuvre des modèles, les changements à l'étendue des modèles ou tout autre changement visant à régler les dysfonctionnements liés aux modèles.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>La rubrique « Mises à jour des modèles » inclut la mise en œuvre des nouveaux modèles, les changements à l'étendue des modèles ou tout autre changement visant à régler les dysfonctionnements liés aux modèles.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>OUI — l'ajout de la précision que les modèles mis en œuvre sont nouveaux est une modification significative au t2. Ce changement impacte directement la méthodologie de gestion des risques, ce qui est pertinent pour le thème AMF MODIFICATION_METHODOLOGIE. La surveillance doit intégrer cette modification dans l'analyse des modèles de gestion des risques.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Risque de crédit</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Entre le 2 mars 2022 et le 12 juillet 2023, la Banque du Canada avait relevé son taux directeur à dix reprises, ce dernier passant de 0,25 % à 5 %. Cette hausse rapide des taux, qui avait pour but principal de contrer l'inflation au Canada, continue d'exercer une pression sur la capacité des titulaires d'emprunts à effectuer leurs versements, notamment celle des titulaires d'hypothèques à taux variable ou dont le terme arrive à échéance. Dans ses six dernières annonces qui ont eu lieu entre le 5 juin 2024 et le 29 janvier 2025, la Banque du Canada a abaissé son taux directeur, le faisant passer de 5 % à 3 %.</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Entre le 2 mars 2022 et le 12 juillet 2023, la Banque du Canada avait relevé son taux directeur à dix reprises, ce dernier passant de 0,25 % à 5 %. Cette hausse rapide des taux, qui avait pour but principal de contrer l'inflation au Canada, continue d'exercer une pression sur la capacité des titulaires d'emprunts à effectuer leurs versements, notamment celle des titulaires d'hypothèques dont le terme est arrivé à échéance dans les derniers mois. Dans ses huit dernières annonces qui ont eu lieu entre le 5 juin 2024 et le 16 avril 2025, la Banque du Canada a abaissé son taux directeur, le faisant passer de 5 % à 2,75 %.</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Au cours du trimestre terminé le 31 janvier 2025, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Au cours du trimestre et du semestre terminés le 30 avril 2025, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>NON — la mise à jour des détails sur les annonces de la Banque du Canada, incluant le nombre d'annonces, les dates et le taux final, constitue une variation chiffrée propre à la banque. Ces informations ne modifient pas la substance des divulgations réglementaires ou méthodologiques. Elles ne touchent pas non plus aux thèmes AMF identifiés, et ne nécessitent donc aucune action particulière de la part de l'analyste.</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Exposition maximale au risque de crédit selon les catégories d'actifs de Bâle (1)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Premier trimestre 2025 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Premier trimestre 2025 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Deuxième trimestre 2025 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Deuxième trimestre 2025 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>NON — le changement de référence des documents du premier au deuxième trimestre est une mise à jour de routine. Cela ne constitue pas une nouvelle idée car il n'y a pas de modification substantielle des exigences réglementaires ou des méthodologies. Ce type de mise à jour est attendu dans le cadre des cycles de reporting trimestriels et ne nécessite aucune action.</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>VaR des portefeuilles de négociation (1) (2)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>La moyenne de la VaR totale des portefeuilles de négociation a augmenté, passant de 7,9 M$ à 12,1 M$ entre le quatrième trimestre de 2024 et le premier trimestre de 2025, principalement en raison d'une hausse du risque de taux d'intérêt.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>La moyenne de la VaR totale des portefeuilles de négociation est demeurée stable entre le premier trimestre et le deuxième trimestre de 2025.</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>NON — la modification de la mesure de risque de marché totale, passant d'une augmentation à une stabilité, est une variation chiffrée propre à la banque. Elle ne modifie pas la méthodologie ou les exigences réglementaires et ne touche pas aux thèmes AMF. Ce changement est une mise à jour quantitative attendue et ne nécessite aucune action.</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 31 janvier 2025 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 30 avril 2025 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>NON — la mise à jour de la date de référence pour la variation trimestrielle des sorties de trésorerie est une variation chiffrée propre à la banque. Elle ne modifie pas les hypothèses ou les exigences réglementaires. Ce type de mise à jour est attendu dans les rapports financiers et ne nécessite aucune action particulière.</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Ratio structurel de liquidité à long terme</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 31 janvier 2025 est de 123 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 30 avril 2025 est de 127 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>NON — la mise à jour de la date de référence et du pourcentage du NSFR est une variation chiffrée propre à la banque. Elle ne modifie pas les exigences réglementaires ou la méthodologie de calcul. Ce changement est une mise à jour quantitative attendue et ne nécessite aucune action particulière.</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 31 janvier 2025, ainsi que les données comparatives au 31 octobre 2024. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 30 avril 2025, ainsi que les données comparatives au 31 octobre 2024. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>NON — la modification de la date des échéances contractuelles résiduelles est une variation chiffrée propre à la banque. Elle ne modifie pas la méthodologie ou les exigences réglementaires. Ce changement est une mise à jour de routine et ne nécessite aucune action particulière de la part de l'analyste.</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de ses clients représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de sa clientèle représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>NON — le remplacement du terme 'ses clients' par 'sa clientèle' est une reformulation mineure. Il n'y a pas de changement de fond dans la divulgation des engagements hors bilan. Ce type de modification éditoriale ne touche pas aux thèmes AMF et ne nécessite aucune action particulière.</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Divulgation d'information sur les risques</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Le Rapport annuel 2024, le Rapport aux actionnaires - Premier trimestre 2025 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Le Rapport annuel 2024, le Rapport aux actionnaires - Deuxième trimestre 2025 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>NON — le changement du rapport aux actionnaires du premier au deuxième trimestre est une mise à jour de routine. Cela ne constitue pas une nouvelle idée car il n'y a pas de modification substantielle des exigences réglementaires ou des méthodologies. Ce type de mise à jour est attendu dans le cadre des cycles de reporting trimestriels et ne nécessite aucune action.</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Accord de Bâle</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>La ligne directrice Capacité totale d'absorption des pertes (Total Loss Absorbing Capacity ou TLAC) du BSIF, qui s'applique à toutes les BISI dans le cadre des règlements sur la recapitalisation interne du gouvernement fédéral, vise à faire en sorte qu'une BISI dispose d'une capacité d'absorption des pertes suffisante pour soutenir sa recapitalisation interne dans le cas peu probable où elle deviendrait non viable. La TLAC disponible comprend le total des fonds propres ainsi que certaines dettes de premier rang non garanties qui satisfont tous les critères d'admissibilité à la ligne directrice TLAC du BSIF. Le BSIF exige des BISI qu'elles maintiennent un ratio TLAC fondé sur les risques d'au moins 25,0 % (incluant la RSI) de l'actif pondéré en fonction des risques et un ratio de levier TLAC d'au moins 7,25 %. Le ratio TLAC se calcule en divisant la TLAC disponible par l'actif pondéré en fonction des risques et le ratio de levier TLAC se calcule en divisant la TLAC disponible par l'exposition totale. Au 31 janvier 2025, la valeur des éléments de passif en circulation faisant l'objet de règlements sur la conversion aux fins de la recapitalisation interne s'élève à 23,8 G$ (23,5 G$ au 31 octobre 2024).</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>La ligne directrice Capacité totale d'absorption des pertes (Total Loss Absorbing Capacity ou TLAC) du BSIF, qui s'applique à toutes les BISI dans le cadre des règlements sur la recapitalisation interne du gouvernement fédéral, vise à faire en sorte qu'une BISI dispose d'une capacité d'absorption des pertes suffisante pour soutenir sa recapitalisation interne dans le cas peu probable où elle deviendrait non viable. La TLAC disponible comprend le total des fonds propres ainsi que certaines dettes de premier rang non garanties qui satisfont tous les critères d'admissibilité à la ligne directrice TLAC du BSIF. Le BSIF exige des BISI qu'elles maintiennent un ratio TLAC fondé sur les risques d'au moins 25,0 % (incluant la RSI) de l'actif pondéré en fonction des risques et un ratio de levier TLAC d'au moins 7,25 %. Le ratio TLAC se calcule en divisant la TLAC disponible par l'actif pondéré en fonction des risques et le ratio de levier TLAC se calcule en divisant la TLAC disponible par l'exposition totale. Au 30 avril 2025, la valeur des éléments de passif en circulation faisant l'objet de règlements sur la conversion aux fins de la recapitalisation interne s'élève à 23,4 G$ (23,5 G$ au 31 octobre 2024).</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>NON — la modification concerne uniquement la date de référence pour la valeur des éléments de passif en circulation, passant de janvier à avril. Il s'agit d'une variation chiffrée propre à la banque sans implication réglementaire ou méthodologique. Aucun thème AMF n'est touché, et cela ne constitue pas une nouvelle idée pour la surveillance prudentielle.</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Dividendes</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Le 25 février 2025, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,14 $ par action ordinaire, payable le 1 er mai 2025 aux actionnaires inscrits le 31 mars 2025.</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Le 27 mai 2025, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,18 $ par action ordinaire, en hausse de 4 cents ou 3,4 %, payable le 1 er août 2025 aux actionnaires inscrits le 30 juin 2025.</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>NON — la modification concerne uniquement la date de déclaration des dividendes et le montant du dividende par action ordinaire, qui a augmenté de 4 cents. Il s'agit d'une variation chiffrée propre à la banque sans implication réglementaire ou méthodologique. Aucun thème AMF n'est touché, et cela ne constitue pas une nouvelle idée pour la surveillance prudentielle.</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Au 21 février 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 216 059 et le nombre d'options en cours est de 11 778 661.</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Au 23 mai 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 340 763 et le nombre d'options en cours est de 11 619 774.</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>NON — la modification concerne uniquement la mise à jour des chiffres des actions ordinaires et des options en circulation. Il s'agit d'une variation chiffrée propre à la banque sans implication réglementaire ou méthodologique. Aucun thème AMF n'est touché, et cela ne constitue pas une nouvelle idée pour la surveillance prudentielle.</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 264 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 78,7 % selon le nombre d'actions ordinaires de la Banque en circulation au 31 janvier 2025.</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 472 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 79,0 % selon le nombre d'actions ordinaires de la Banque en circulation au 30 avril 2025.</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>NON — la modification concerne uniquement la mise à jour des chiffres de conversion maximale et de l'effet dilutif. Il s'agit d'une variation chiffrée propre à la banque sans implication réglementaire ou méthodologique. Aucun thème AMF n'est touché, et cela ne constitue pas une nouvelle idée pour la surveillance prudentielle.</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Au cours du trimestre terminé le 31 janvier 2025, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Au cours du trimestre et du semestre terminés le 30 avril 2025, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>NON — la modification concerne uniquement l'ajout de la mention du respect des exigences pour le semestre. Il s'agit d'une reformulation mineure sans implication réglementaire ou méthodologique. Aucun thème AMF n'est touché, et cela ne constitue pas une nouvelle idée pour la surveillance prudentielle.</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 ajoute la mention du respect des exigences pour le semestre, sans modification de fond.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale d'un chiffre propre à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/text_comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/text_comparison.xlsx
@@ -842,15 +842,111 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>Le 3 février 2025, lors de la clôture de l'acquisition de CWB, la Banque a émis un total de 50 272 878 actions ordinaires, pour un produit brut de 6,3 G$.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information ajoutée, capital réglementaire.
+Ce qui change : Le T2 ajoute des informations sur l'émission de 50 272 878 actions ordinaires pour un produit brut de 6,3 G$ lors de l'acquisition de CWB.
+Pertinence métier : Ce changement met l'accent sur l'évolution de la structure de capital de la banque suite à une acquisition majeure. L'émission d'actions ordinaires modifie la composition du capital réglementaire et peut influencer la perception de la solidité financière de la banque par les régulateurs et les investisseurs.
+Point de surveillance : Capital réglementaire — Le changement indique une augmentation du capital par émission d'actions, ce qui peut affecter les ratios de capital et la comparabilité avec les pairs.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>c'et pas un vrai changement pas important vraiment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Activités de gestion</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Le 3 février 2025, dans le cadre de l'acquisition de CWB, la Banque a acquis les obligations liées aux dettes subordonnées de CWB pour un montant total de 525 M$, qui incluait une débenture de 125 M$ portant intérêt à 4,840 % et échéant le 29 juin 2030 (le 2 mai 2025, la Banque a informé les détenteurs de son intention de racheter les débentures le 29 juin 2025, à un prix de rachat égal au capital impayé plus l'intérêt couru et impayé), une débenture de 150 M$ portant intérêt à 5,937 % et échéant le 22 décembre 2032 et une débenture de 250 M$ portant intérêt à 5,949 % et échéant le 29 janvier 2034. Comme les débentures respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information ajoutée, fonds propres réglementaires.
+Ce qui change : Le T2 ajoute des informations sur l'acquisition de 525 M$ d'obligations liées aux dettes subordonnées de CWB, incluant des débentures portant intérêt à des taux spécifiques.
+Pertinence métier : Ce changement met l'accent sur l'intégration de nouveaux instruments de fonds propres dans le calcul des fonds propres réglementaires. L'acquisition de ces obligations peut influencer la structure de capital de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la composition des fonds propres, ce qui peut affecter les ratios de capital et la comparabilité avec les pairs.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>oui une nouvelle idee mais vraiment pas pertinant quand meme pour nous</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Activités de gestion</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>Le 20 février 2025, il y a eu un échange de la totalité des actions privilégiées de premier rang, série 5 et série 9, émises et en circulation de CWB, contre des actions privilégiées de premier rang essentiellement équivalentes de la Banque Nationale, série 47 et série 49, donnant droit à un dividende non cumulatif à taux rajusté tous les cinq ans, portant intérêt à 6,371 % et 7,651 %. La Banque a échangé 10 000 000 actions privilégiées pour un montant total de 264 M$. Comme les actions privilégiées, série 47 et série 49, respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Information ajoutée, fonds propres réglementaires.
@@ -859,50 +955,258 @@
 Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la composition des fonds propres, ce qui peut affecter les ratios de capital et la comparabilité avec les pairs.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Si un événement déclencheur faisant intervenir les clauses FPUNV devait se produire, toutes les actions privilégiées et les BCRL de la Banque ainsi que les billets à moyen terme échéant le 16 août 2032, le 15 février 2034 et le 15 février 2035, qui sont des instruments de fonds propres assortis d'une clause FPUNV, seraient convertis en actions ordinaires de la Banque selon une formule de conversion automatique, à un prix de conversion correspondant au plus élevé des montants suivants : i) un prix plancher contractuel de 5,00 $; ii) le cours du marché des actions ordinaires de la Banque à la date de l'événement déclencheur (cours moyen pondéré sur 10 jours).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Si un événement déclencheur faisant intervenir les clauses FPUNV devait se produire, toutes les actions privilégiées et les BCRL de la Banque ainsi que les billets à moyen terme et les débentures subordonnées, qui sont des instruments de fonds propres assortis d'une clause FPUNV, seraient convertis en actions ordinaires de la Banque selon une formule de conversion automatique, à un prix de conversion correspondant au plus élevé des montants suivants : i) un prix plancher contractuel de 5,00 $; ii) le cours du marché des actions ordinaires de la Banque à la date de l'événement déclencheur (cours moyen pondéré sur 10 jours).</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Information ajoutée, fonds propres réglementaires.
+Ce qui change : Le T2 ajoute les débentures subordonnées à la liste des instruments convertibles en actions ordinaires en cas de déclenchement des clauses FPUNV.
+Pertinence métier : Ce changement met l'accent sur la transparence de la divulgation concernant les fonds propres réglementaires. L'ajout de ces débentures modifie la perception de la solidité financière de la banque et sa capacité à absorber les pertes en cas de crise.
+Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la composition des instruments convertibles, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>L'actif pondéré en fonction des risques a augmenté de 7,5 G$ pour s'établir à 148,5 G$ au 31 janvier 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de la croissance organique de l'actif pondéré en fonction des risques, de la variation du taux de change et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>L'actif pondéré en fonction des risques a augmenté de 41,8 G$ pour s'établir à 182,8 G$ au 30 avril 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de l'inclusion de CWB, ainsi que de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, fonds propres réglementaires.
+Ce qui change : Le T2 ajoute l'inclusion de CWB comme facteur d'augmentation de l'actif pondéré en fonction des risques, absent au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Fonds propres réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Le ratio de levier en date du 31 janvier 2025 s'établit à 4,3 %, comparativement à 4,4 % au 31 octobre 2024. La baisse du ratio de levier s'explique essentiellement par l'augmentation de l'exposition totale, en partie contrebalancée par la croissance des fonds propres de catégorie 1.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Le ratio de levier en date du 30 avril 2025 s'établit à 4,7 %, comparativement à 4,4 % au 31 octobre 2024. L'augmentation du ratio de levier s'explique essentiellement par la croissance des fonds propres de catégorie 1 en lien avec les actions ordinaires émises dans le cadre de l'acquisition de CWB, en partie contrebalancée par l'augmentation de l'exposition totale.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, ratio ou seuil prudentiel.
+Ce qui change : Le T2 ajoute l'acquisition de CWB comme facteur influençant le ratio de levier, absent au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Ratios réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Au 31 janvier 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 31,2 % et à 8,7 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. Le ratio TLAC est demeuré stable et l'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours du premier trimestre de 2025.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Au 30 avril 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 28,2 % et à 8,8 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. L'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours de la période. Cependant, la croissance de l'actif pondéré en fonction des risques, principalement attribuable à l'inclusion de CWB, a largement compensé ces émissions, ce qui a entraîné une diminution du ratio TLAC.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, ratio ou seuil prudentiel.
+Ce qui change : Le T2 ajoute l'inclusion de CWB comme facteur influençant le ratio TLAC, absent au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
+Point de surveillance : Ratios réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Activités de gestion</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Le 17 février 2025, soit le premier jour ouvrable suivant la date de rachat du 15 février 2025, la Banque a terminé le rachat de la totalité des actions privilégiées de premier rang à dividende non cumulatif à taux rajusté tous les cinq ans, série 32, émises et en circulation. Tel que prévu dans les conditions relatives aux actions, le prix de rachat était de 25,00 $ l'action, plus les dividendes périodiques déclarés et impayés. La Banque a racheté 12 000 000 actions privilégiées série 32 pour un prix total de 300 M$. Ces instruments ont été exclus du calcul des ratios de fonds propres au 31 janvier 2025.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Le 17 février 2025, soit le premier jour ouvrable suivant la date de rachat du 15 février 2025, la Banque a terminé le rachat de la totalité des actions privilégiées de premier rang à dividende non cumulatif à taux rajusté tous les cinq ans, série 32, émises et en circulation. Tel que prévu dans les conditions relatives aux actions, le prix de rachat était de 25,00 $ l'action, plus les dividendes périodiques déclarés et impayés. La Banque a racheté 12 000 000 actions privilégiées série 32 pour un prix total de 300 M$.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Information retirée, fonds propres réglementaires.
@@ -911,313 +1215,9 @@
 Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la divulgation sur la composition des fonds propres, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Non pas un vrai changement</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Si un événement déclencheur faisant intervenir les clauses FPUNV devait se produire, toutes les actions privilégiées et les BCRL de la Banque ainsi que les billets à moyen terme échéant le 16 août 2032, le 15 février 2034 et le 15 février 2035, qui sont des instruments de fonds propres assortis d'une clause FPUNV, seraient convertis en actions ordinaires de la Banque selon une formule de conversion automatique, à un prix de conversion correspondant au plus élevé des montants suivants : i) un prix plancher contractuel de 5,00 $; ii) le cours du marché des actions ordinaires de la Banque à la date de l'événement déclencheur (cours moyen pondéré sur 10 jours).</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Si un événement déclencheur faisant intervenir les clauses FPUNV devait se produire, toutes les actions privilégiées et les BCRL de la Banque ainsi que les billets à moyen terme et les débentures subordonnées, qui sont des instruments de fonds propres assortis d'une clause FPUNV, seraient convertis en actions ordinaires de la Banque selon une formule de conversion automatique, à un prix de conversion correspondant au plus élevé des montants suivants : i) un prix plancher contractuel de 5,00 $; ii) le cours du marché des actions ordinaires de la Banque à la date de l'événement déclencheur (cours moyen pondéré sur 10 jours).</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Information ajoutée, fonds propres réglementaires.
-Ce qui change : Le T2 ajoute les débentures subordonnées à la liste des instruments convertibles en actions ordinaires en cas de déclenchement des clauses FPUNV.
-Pertinence métier : Ce changement met l'accent sur la transparence de la divulgation concernant les fonds propres réglementaires. L'ajout de ces débentures modifie la perception de la solidité financière de la banque et sa capacité à absorber les pertes en cas de crise.
-Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la composition des instruments convertibles, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de 7,5 G$ pour s'établir à 148,5 G$ au 31 janvier 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de la croissance organique de l'actif pondéré en fonction des risques, de la variation du taux de change et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de 41,8 G$ pour s'établir à 182,8 G$ au 30 avril 2025, comparativement à 141,0 G$ au 31 octobre 2024. Cette augmentation découle principalement de l'inclusion de CWB, ainsi que de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts. La variation de l'actif pondéré en fonction des risques de la Banque par type de risque est présentée dans le tableau suivant.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Texte de risque modifié, fonds propres réglementaires.
-Ce qui change : Le T2 ajoute l'inclusion de CWB comme facteur d'augmentation de l'actif pondéré en fonction des risques, absent au T1.
-Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
-Point de surveillance : Fonds propres réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Le ratio de levier en date du 31 janvier 2025 s'établit à 4,3 %, comparativement à 4,4 % au 31 octobre 2024. La baisse du ratio de levier s'explique essentiellement par l'augmentation de l'exposition totale, en partie contrebalancée par la croissance des fonds propres de catégorie 1.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Le ratio de levier en date du 30 avril 2025 s'établit à 4,7 %, comparativement à 4,4 % au 31 octobre 2024. L'augmentation du ratio de levier s'explique essentiellement par la croissance des fonds propres de catégorie 1 en lien avec les actions ordinaires émises dans le cadre de l'acquisition de CWB, en partie contrebalancée par l'augmentation de l'exposition totale.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Texte de risque modifié, ratio ou seuil prudentiel.
-Ce qui change : Le T2 ajoute l'acquisition de CWB comme facteur influençant le ratio de levier, absent au T1.
-Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
-Point de surveillance : Ratios réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Au 31 janvier 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 31,2 % et à 8,7 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. Le ratio TLAC est demeuré stable et l'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours du premier trimestre de 2025.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Au 30 avril 2025, le ratio TLAC et le ratio de levier TLAC s'établissent à 28,2 % et à 8,8 %, comparativement à 31,2 % et à 8,6 %, respectivement, au 31 octobre 2024. L'augmentation du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours de la période. Cependant, la croissance de l'actif pondéré en fonction des risques, principalement attribuable à l'inclusion de CWB, a largement compensé ces émissions, ce qui a entraîné une diminution du ratio TLAC.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Texte de risque modifié, ratio ou seuil prudentiel.
-Ce qui change : Le T2 ajoute l'inclusion de CWB comme facteur influençant le ratio TLAC, absent au T1.
-Pertinence métier : Ce changement met l'accent sur l'évolution des facteurs influençant les ratios de capital de la banque. L'ajout de CWB modifie la perception de la solidité financière de la banque et sa capacité à répondre aux exigences réglementaires.
-Point de surveillance : Ratios réglementaires — Le changement indique une modification des facteurs influençant les ratios de capital, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Activités de gestion</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Le 3 février 2025, lors de la clôture de l'acquisition de CWB, la Banque a émis un total de 50 272 878 actions ordinaires, pour un produit brut de 6,3 G$.</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Information ajoutée, capital réglementaire.
-Ce qui change : Le T2 ajoute des informations sur l'émission de 50 272 878 actions ordinaires pour un produit brut de 6,3 G$ lors de l'acquisition de CWB.
-Pertinence métier : Ce changement met l'accent sur l'évolution de la structure de capital de la banque suite à une acquisition majeure. L'émission d'actions ordinaires modifie la composition du capital réglementaire et peut influencer la perception de la solidité financière de la banque par les régulateurs et les investisseurs.
-Point de surveillance : Capital réglementaire — Le changement indique une augmentation du capital par émission d'actions, ce qui peut affecter les ratios de capital et la comparabilité avec les pairs.</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>c'et pas un vrai changement pas important vraiment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Activités de gestion</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Le 3 février 2025, dans le cadre de l'acquisition de CWB, la Banque a acquis les obligations liées aux dettes subordonnées de CWB pour un montant total de 525 M$, qui incluait une débenture de 125 M$ portant intérêt à 4,840 % et échéant le 29 juin 2030 (le 2 mai 2025, la Banque a informé les détenteurs de son intention de racheter les débentures le 29 juin 2025, à un prix de rachat égal au capital impayé plus l'intérêt couru et impayé), une débenture de 150 M$ portant intérêt à 5,937 % et échéant le 22 décembre 2032 et une débenture de 250 M$ portant intérêt à 5,949 % et échéant le 29 janvier 2034. Comme les débentures respectent les exigences relatives aux FPUNV, elles sont admissibles aux fins du calcul des fonds propres réglementaires selon les règles de Bâle III.</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Information ajoutée, fonds propres réglementaires.
-Ce qui change : Le T2 ajoute des informations sur l'acquisition de 525 M$ d'obligations liées aux dettes subordonnées de CWB, incluant des débentures portant intérêt à des taux spécifiques.
-Pertinence métier : Ce changement met l'accent sur l'intégration de nouveaux instruments de fonds propres dans le calcul des fonds propres réglementaires. L'acquisition de ces obligations peut influencer la structure de capital de la banque et sa capacité à répondre aux exigences réglementaires.
-Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la composition des fonds propres, ce qui peut affecter les ratios de capital et la comparabilité avec les pairs.</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>oui une nouvelle idee mais vraiment pas pertinant quand meme pour nous</t>
         </is>
       </c>
     </row>

--- a/outputs/resultats/bnc/2025_t2_vs_2025_t1/text_comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t2_vs_2025_t1/text_comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analyse complète" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analyse complète'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analyse complète'!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADADD"/>
+        <bgColor rgb="00FADADD"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -87,6 +93,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -457,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -623,38 +632,90 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Risque de marché</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Le risque de marché est le risque de pertes financières liées à la variation des prix de marché. La Banque est exposée au risque de marché en raison de sa participation à des activités de négociation, d'investissement et de gestion de l'appariement du bilan. Depuis quelques années, la Banque fait face à un contexte volatil. Le contexte géopolitique, notamment les mesures affectant les relations commerciales entre le Canada et ses partenaires, incluant l'imposition de tarifs et toute mesure de riposte, la guerre russo-ukrainienne ainsi que les affrontements entre Israël et le Hamas, l'inflation, les changements climatiques et les taux d'intérêt élevés continuent à créer des incertitudes.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Le risque de marché est le risque de pertes financières liées à la variation des prix de marché. La Banque est exposée au risque de marché en raison de sa participation à des activités de négociation, d'investissement et de gestion de l'appariement du bilan.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, information retirée.
+Ce qui change : Le T2 retire la description du contexte géopolitique et économique volatile, incluant les mesures commerciales, la guerre russo-ukrainienne, et les affrontements entre Israël et le Hamas, qui étaient mentionnés au T1.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Exigences de communication publique pour les banques d'importance systémique mondiale</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Le CBCB a développé une méthodologie d'évaluation et d'exigence de capacité additionnelle d'absorption des pertes ainsi que des indicateurs utilisés par le CBCB et le Conseil de stabilité financière pour évaluer les banques d'importance systémique mondiale (BISM). Des exigences de communication publique annuelles s'appliquent aux grandes banques actives à l'échelle mondiale.
 La dernière version du préavis du BSIF intitulé Banques d'importance systémique mondiale - Obligations redditionnelles à l'égard de la mise en œuvre des exigences de communication publique pour les BISM au Canada est entrée en vigueur en 2022. Les banques canadiennes, y compris la Banque, qui n'ont pas été désignées BISM et qui ont une exposition totale (telle que calculée par le ratio de levier selon Bâle III) supérieure à l'équivalent de 200 milliards d'euros à la fin de l'exercice sont tenues de publier annuellement les indicateurs. Les indicateurs sont calculés et présentés selon des lignes directrices précises publiées par le CBCB, qui sont mises à jour chaque année. Ainsi, les valeurs obtenues ne sont peut-être pas comparables aux autres mesures présentées dans ce rapport. Le tableau suivant présente les indicateurs utilisés dans la méthode d'évaluation du CBCB permettant d'évaluer les BISM.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Information retirée, exigences réglementaires ou conformité.
@@ -663,63 +724,11 @@
 Point de surveillance : Exigences réglementaires — Le changement indique une modification de la divulgation sur les obligations de communication, ce qui peut affecter la comparabilité avec les pairs et la lecture des pratiques de conformité.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Oui c'est un vrai changment</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Risque de marché</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Le risque de marché est le risque de pertes financières liées à la variation des prix de marché. La Banque est exposée au risque de marché en raison de sa participation à des activités de négociation, d'investissement et de gestion de l'appariement du bilan. Depuis quelques années, la Banque fait face à un contexte volatil. Le contexte géopolitique, notamment les mesures affectant les relations commerciales entre le Canada et ses partenaires, incluant l'imposition de tarifs et toute mesure de riposte, la guerre russo-ukrainienne ainsi que les affrontements entre Israël et le Hamas, l'inflation, les changements climatiques et les taux d'intérêt élevés continuent à créer des incertitudes.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Le risque de marché est le risque de pertes financières liées à la variation des prix de marché. La Banque est exposée au risque de marché en raison de sa participation à des activités de négociation, d'investissement et de gestion de l'appariement du bilan.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Texte de risque modifié, information retirée.
-Ce qui change : Le T2 retire la description du contexte géopolitique et économique volatile, incluant les mesures commerciales, la guerre russo-ukrainienne, et les affrontements entre Israël et le Hamas, qui étaient mentionnés au T1.
-Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
-Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1166,47 +1175,47 @@
       <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Activités de gestion</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Le 17 février 2025, soit le premier jour ouvrable suivant la date de rachat du 15 février 2025, la Banque a terminé le rachat de la totalité des actions privilégiées de premier rang à dividende non cumulatif à taux rajusté tous les cinq ans, série 32, émises et en circulation. Tel que prévu dans les conditions relatives aux actions, le prix de rachat était de 25,00 $ l'action, plus les dividendes périodiques déclarés et impayés. La Banque a racheté 12 000 000 actions privilégiées série 32 pour un prix total de 300 M$. Ces instruments ont été exclus du calcul des ratios de fonds propres au 31 janvier 2025.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Le 17 février 2025, soit le premier jour ouvrable suivant la date de rachat du 15 février 2025, la Banque a terminé le rachat de la totalité des actions privilégiées de premier rang à dividende non cumulatif à taux rajusté tous les cinq ans, série 32, émises et en circulation. Tel que prévu dans les conditions relatives aux actions, le prix de rachat était de 25,00 $ l'action, plus les dividendes périodiques déclarés et impayés. La Banque a racheté 12 000 000 actions privilégiées série 32 pour un prix total de 300 M$.</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Information retirée, fonds propres réglementaires.
@@ -1215,54 +1224,106 @@
 Point de surveillance : Fonds propres réglementaires — Le changement indique une modification de la divulgation sur la composition des fonds propres, ce qui peut affecter la comparabilité avec les pairs et la lecture des ratios de capital.</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Non pas un vrai changement</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Risque de crédit</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Entre le 2 mars 2022 et le 12 juillet 2023, la Banque du Canada avait relevé son taux directeur à dix reprises, ce dernier passant de 0,25 % à 5 %. Cette hausse rapide des taux, qui avait pour but principal de contrer l'inflation au Canada, continue d'exercer une pression sur la capacité des titulaires d'emprunts à effectuer leurs versements, notamment celle des titulaires d'hypothèques à taux variable ou dont le terme arrive à échéance. Dans ses six dernières annonces qui ont eu lieu entre le 5 juin 2024 et le 29 janvier 2025, la Banque du Canada a abaissé son taux directeur, le faisant passer de 5 % à 3 %.</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Entre le 2 mars 2022 et le 12 juillet 2023, la Banque du Canada avait relevé son taux directeur à dix reprises, ce dernier passant de 0,25 % à 5 %. Cette hausse rapide des taux, qui avait pour but principal de contrer l'inflation au Canada, continue d'exercer une pression sur la capacité des titulaires d'emprunts à effectuer leurs versements, notamment celle des titulaires d'hypothèques dont le terme est arrivé à échéance dans les derniers mois. Dans ses huit dernières annonces qui ont eu lieu entre le 5 juin 2024 et le 16 avril 2025, la Banque du Canada a abaissé son taux directeur, le faisant passer de 5 % à 2,75 %.</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 met à jour le nombre d'annonces de la Banque du Canada, passant de six à huit, et ajuste la période de référence. Ces changements sont purement factuels et ne modifient pas la substance de la divulgation.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale des annonces de politique monétaire. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Exposition maximale au risque de crédit selon les catégories d'actifs de Bâle (1)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Premier trimestre 2025 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Premier trimestre 2025 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Deuxième trimestre 2025 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Deuxième trimestre 2025 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de période de référence.
@@ -1271,50 +1332,50 @@
 Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>VaR des portefeuilles de négociation (1) (2)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>La moyenne de la VaR totale des portefeuilles de négociation a augmenté, passant de 7,9 M$ à 12,1 M$ entre le quatrième trimestre de 2024 et le premier trimestre de 2025, principalement en raison d'une hausse du risque de taux d'intérêt.</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>La moyenne de la VaR totale des portefeuilles de négociation est demeurée stable entre le premier trimestre et le deuxième trimestre de 2025.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
@@ -1323,50 +1384,102 @@
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Ratio de liquidité à court terme</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Le tableau de la page suivante présente les positions moyennes du LCR calculées à partir des observations quotidiennes du trimestre. Le LCR moyen de la Banque au cours du trimestre terminé le 31 janvier 2025 est de 154 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à court terme de la Banque est solide.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Le tableau de la page suivante présente les positions moyennes du LCR calculées à partir des observations quotidiennes du trimestre. Le LCR moyen de la Banque au cours du trimestre terminé le 30 avril 2025 est de 166 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à court terme de la Banque est solide.</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 met à jour la date et le pourcentage du LCR moyen, passant de janvier à avril et de 154 % à 166 %. Ce changement est purement factuel et ne modifie pas la substance de la divulgation.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale des mesures de liquidité propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Au 31 janvier 2025, les actifs liquides de niveau 1 représentent 84 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Au 30 avril 2025, les actifs liquides de niveau 1 représentent 84 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de date de référence.
@@ -1375,50 +1488,50 @@
 Point de surveillance : Mise à jour de date — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 31 janvier 2025 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 30 avril 2025 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de date de référence.
@@ -1427,50 +1540,50 @@
 Point de surveillance : Mise à jour de date — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Ratio structurel de liquidité à long terme</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 31 janvier 2025 est de 123 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 30 avril 2025 est de 127 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
@@ -1479,50 +1592,50 @@
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 31 janvier 2025, ainsi que les données comparatives au 31 octobre 2024. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 30 avril 2025, ainsi que les données comparatives au 31 octobre 2024. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de date de référence.
@@ -1531,50 +1644,50 @@
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de ses clients représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de sa clientèle représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Reformulation mineure.
@@ -1583,50 +1696,50 @@
 Point de surveillance : Reformulation mineure — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Divulgation d'information sur les risques</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Le Rapport annuel 2024, le Rapport aux actionnaires - Premier trimestre 2025 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Le Rapport annuel 2024, le Rapport aux actionnaires - Deuxième trimestre 2025 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de période de référence.
@@ -1635,50 +1748,102 @@
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Accord de Bâle</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>La ligne directrice Capacité totale d'absorption des pertes (Total Loss Absorbing Capacity ou TLAC) du BSIF, qui s'applique à toutes les BISI dans le cadre des règlements sur la recapitalisation interne du gouvernement fédéral, vise à faire en sorte qu'une BISI dispose d'une capacité d'absorption des pertes suffisante pour soutenir sa recapitalisation interne dans le cas peu probable où elle deviendrait non viable. La TLAC disponible comprend le total des fonds propres ainsi que certaines dettes de premier rang non garanties qui satisfont tous les critères d'admissibilité à la ligne directrice TLAC du BSIF. Le BSIF exige des BISI qu'elles maintiennent un ratio TLAC fondé sur les risques d'au moins 25,0 % (incluant la RSI) de l'actif pondéré en fonction des risques et un ratio de levier TLAC d'au moins 7,25 %. Le ratio TLAC se calcule en divisant la TLAC disponible par l'actif pondéré en fonction des risques et le ratio de levier TLAC se calcule en divisant la TLAC disponible par l'exposition totale. Au 31 janvier 2025, la valeur des éléments de passif en circulation faisant l'objet de règlements sur la conversion aux fins de la recapitalisation interne s'élève à 23,8 G$ (23,5 G$ au 31 octobre 2024).</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>La ligne directrice Capacité totale d'absorption des pertes (Total Loss Absorbing Capacity ou TLAC) du BSIF, qui s'applique à toutes les BISI dans le cadre des règlements sur la recapitalisation interne du gouvernement fédéral, vise à faire en sorte qu'une BISI dispose d'une capacité d'absorption des pertes suffisante pour soutenir sa recapitalisation interne dans le cas peu probable où elle deviendrait non viable. La TLAC disponible comprend le total des fonds propres ainsi que certaines dettes de premier rang non garanties qui satisfont tous les critères d'admissibilité à la ligne directrice TLAC du BSIF. Le BSIF exige des BISI qu'elles maintiennent un ratio TLAC fondé sur les risques d'au moins 25,0 % (incluant la RSI) de l'actif pondéré en fonction des risques et un ratio de levier TLAC d'au moins 7,25 %. Le ratio TLAC se calcule en divisant la TLAC disponible par l'actif pondéré en fonction des risques et le ratio de levier TLAC se calcule en divisant la TLAC disponible par l'exposition totale. Au 30 avril 2025, la valeur des éléments de passif en circulation faisant l'objet de règlements sur la conversion aux fins de la recapitalisation interne s'élève à 23,4 G$ (23,5 G$ au 31 octobre 2024).</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour quantitative propre à la banque.
+Ce qui change : Le T2 met à jour la date et la valeur des éléments de passif en circulation, sans modification de fond.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète l'évolution normale d'un chiffre propre à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Dividendes</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Le 25 février 2025, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,14 $ par action ordinaire, payable le 1 er mai 2025 aux actionnaires inscrits le 31 mars 2025.</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Le 27 mai 2025, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,18 $ par action ordinaire, en hausse de 4 cents ou 3,4 %, payable le 1 er août 2025 aux actionnaires inscrits le 30 juin 2025.</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
@@ -1687,50 +1852,50 @@
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Au 21 février 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 216 059 et le nombre d'options en cours est de 11 778 661.</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Au 23 mai 2025, le nombre d'actions ordinaires en circulation se chiffre à 391 340 763 et le nombre d'options en cours est de 11 619 774.</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
@@ -1739,50 +1904,50 @@
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 264 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 78,7 % selon le nombre d'actions ordinaires de la Banque en circulation au 31 janvier 2025.</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 472 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 79,0 % selon le nombre d'actions ordinaires de la Banque en circulation au 30 avril 2025.</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
@@ -1791,50 +1956,50 @@
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,6 %, à 15,5 % et à 17,1 % au 31 janvier 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Le ratio des fonds propres CET1 et le ratio des fonds propres de catégorie 1 sont en baisse comparativement au 31 octobre 2024, alors que le ratio du total des fonds propres est légèrement en hausse. La croissance organique de l'actif pondéré en fonction des risques a eu un impact défavorable sur les ratios, atténué par le résultat net, déduction faite des dividendes. Le rachat d'actions privilégiées pour un montant de 300 M$ effectué le 17 février 2025, déjà exclu du calcul des ratios des fonds propres au 31 janvier 2025, a eu un impact défavorable sur le ratio des fonds propres de catégorie 1, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025, a eu un impact favorable sur le ratio du total des fonds propres.</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,4 %, à 15,1 % et à 16,9 % au 30 avril 2025, comparativement à des ratios de 13,7 %, de 15,9 % et de 17,0 %, respectivement, au 31 octobre 2024. Tous les ratios des fonds propres sont en baisse comparativement au 31 octobre 2024. La croissance de l'actif pondéré en fonction des risques, principalement due à l'inclusion de CWB, a eu un impact défavorable sur les ratios, un impact atténué par les actions ordinaires émises dans le cadre de l'acquisition de CWB et par le résultat net, déduction faite des dividendes. De plus, le rachat d'actions privilégiées effectué le 17 février 2025 atténué par l'échange des actions privilégiées de CWB contre des actions privilégiées de la Banque le 20 février 2025 a eu un impact défavorable sur les ratios des fonds propres de catégorie 1 et du total des fonds propres, alors que l'émission de 1,0 G$ des billets à moyen terme, le 13 janvier 2025 et les obligations liées aux dettes subordonnées de CWB de 525 M$ ont eu un impact favorable sur le ratio du total des fonds propres.</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
@@ -1843,50 +2008,50 @@
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Au cours du trimestre terminé le 31 janvier 2025, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Au cours du trimestre et du semestre terminés le 30 avril 2025, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
@@ -1895,10 +2060,10 @@
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>